--- a/static_files/manual.xlsx
+++ b/static_files/manual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KEC\HL7-Helper\static_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DD1A85-3C29-49AC-B67F-A22698E93A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAC81C1-FD59-446A-AC65-48D2E46CB81C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{ED8BEDC3-DBCC-4188-B4B2-8E63CDEE6B29}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{ED8BEDC3-DBCC-4188-B4B2-8E63CDEE6B29}"/>
   </bookViews>
   <sheets>
     <sheet name="Uebersicht" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="264">
   <si>
     <t>Diacos</t>
   </si>
@@ -886,12 +886,15 @@
   <si>
     <t>?</t>
   </si>
+  <si>
+    <t>Todos</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -975,6 +978,14 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1002,7 +1013,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1032,32 +1043,24 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1424,9 +1427,12 @@
       <c r="F1" s="7" t="s">
         <v>43</v>
       </c>
+      <c r="G1" s="7" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1446,7 +1452,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1464,7 +1470,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1481,7 +1487,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1499,7 +1505,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1517,7 +1523,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1537,7 +1543,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1552,12 +1558,12 @@
       <c r="F8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="17" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1574,7 +1580,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1588,7 +1594,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1605,7 +1611,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1622,14 +1628,19 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="E13" s="9"/>
+      <c r="E13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E14" s="9"/>
@@ -1647,1457 +1658,1457 @@
   <dimension ref="A1:Q113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" style="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" style="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="15">
         <v>1</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="15">
         <v>1</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="20">
-        <v>2</v>
-      </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
+      <c r="C4" s="15">
+        <v>2</v>
+      </c>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="20">
-        <v>2</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
+      <c r="C6" s="15">
+        <v>2</v>
+      </c>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="20">
-        <v>2</v>
-      </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
+      <c r="C7" s="15">
+        <v>2</v>
+      </c>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" t="s">
         <v>127</v>
       </c>
-      <c r="C8" s="20">
-        <v>2</v>
-      </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
+      <c r="C8" s="15">
+        <v>2</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="20">
-        <v>2</v>
-      </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
+      <c r="C9" s="15">
+        <v>2</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" t="s">
         <v>131</v>
       </c>
-      <c r="C10" s="20">
-        <v>2</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
+      <c r="C10" s="15">
+        <v>2</v>
+      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" t="s">
         <v>133</v>
       </c>
-      <c r="C11" s="20">
-        <v>2</v>
-      </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
+      <c r="C11" s="15">
+        <v>2</v>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="20">
-        <v>2</v>
-      </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
+      <c r="C12" s="15">
+        <v>2</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="20">
-        <v>2</v>
-      </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
+      <c r="C13" s="15">
+        <v>2</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="20">
-        <v>2</v>
-      </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
+      <c r="C14" s="15">
+        <v>2</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" t="s">
         <v>141</v>
       </c>
-      <c r="C15" s="20">
-        <v>2</v>
-      </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
+      <c r="C15" s="15">
+        <v>2</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" t="s">
         <v>143</v>
       </c>
-      <c r="C16" s="20">
-        <v>2</v>
-      </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
+      <c r="C16" s="15">
+        <v>2</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" t="s">
         <v>145</v>
       </c>
-      <c r="C17" s="20">
-        <v>2</v>
-      </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
+      <c r="C17" s="15">
+        <v>2</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="20">
-        <v>2</v>
-      </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
+      <c r="C18" s="15">
+        <v>2</v>
+      </c>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" t="s">
         <v>149</v>
       </c>
-      <c r="C19" s="20">
-        <v>2</v>
-      </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
+      <c r="C19" s="15">
+        <v>2</v>
+      </c>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" t="s">
         <v>151</v>
       </c>
-      <c r="C20" s="20">
-        <v>2</v>
-      </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
+      <c r="C20" s="15">
+        <v>2</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" t="s">
         <v>153</v>
       </c>
-      <c r="C21" s="20">
-        <v>2</v>
-      </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
+      <c r="C21" s="15">
+        <v>2</v>
+      </c>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" t="s">
         <v>155</v>
       </c>
-      <c r="C22" s="20">
-        <v>2</v>
-      </c>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
+      <c r="C22" s="15">
+        <v>2</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" t="s">
         <v>157</v>
       </c>
-      <c r="C23" s="20">
-        <v>2</v>
-      </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
+      <c r="C23" s="15">
+        <v>2</v>
+      </c>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" t="s">
         <v>159</v>
       </c>
-      <c r="C24" s="20">
-        <v>2</v>
-      </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
+      <c r="C24" s="15">
+        <v>2</v>
+      </c>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" t="s">
         <v>161</v>
       </c>
-      <c r="C25" s="20">
-        <v>2</v>
-      </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
+      <c r="C25" s="15">
+        <v>2</v>
+      </c>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+      <c r="N25" s="16"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="16"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" t="s">
         <v>163</v>
       </c>
-      <c r="C26" s="20">
-        <v>2</v>
-      </c>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
+      <c r="C26" s="15">
+        <v>2</v>
+      </c>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="16"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" t="s">
         <v>165</v>
       </c>
-      <c r="C27" s="20">
-        <v>2</v>
-      </c>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
+      <c r="C27" s="15">
+        <v>2</v>
+      </c>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="16"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="20">
+      <c r="C28" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" t="s">
         <v>189</v>
       </c>
-      <c r="C29" s="20">
+      <c r="C29" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" t="s">
         <v>191</v>
       </c>
-      <c r="C30" s="20">
+      <c r="C30" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" t="s">
         <v>193</v>
       </c>
-      <c r="C31" s="20">
+      <c r="C31" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" t="s">
         <v>195</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" t="s">
         <v>197</v>
       </c>
-      <c r="C33" s="20">
+      <c r="C33" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" t="s">
         <v>199</v>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" t="s">
         <v>201</v>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" t="s">
         <v>203</v>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" t="s">
         <v>205</v>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" t="s">
         <v>207</v>
       </c>
-      <c r="C38" s="20">
+      <c r="C38" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" t="s">
         <v>209</v>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" t="s">
         <v>211</v>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" t="s">
         <v>213</v>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" t="s">
         <v>215</v>
       </c>
-      <c r="C42" s="20">
+      <c r="C42" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" t="s">
         <v>217</v>
       </c>
-      <c r="C43" s="20">
+      <c r="C43" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" t="s">
         <v>219</v>
       </c>
-      <c r="C44" s="20">
+      <c r="C44" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" t="s">
         <v>221</v>
       </c>
-      <c r="C45" s="20">
+      <c r="C45" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" t="s">
         <v>223</v>
       </c>
-      <c r="C46" s="20">
+      <c r="C46" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" t="s">
         <v>225</v>
       </c>
-      <c r="C47" s="20">
+      <c r="C47" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B48" t="s">
         <v>227</v>
       </c>
-      <c r="C48" s="20">
+      <c r="C48" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="B49" t="s">
         <v>229</v>
       </c>
-      <c r="C49" s="20">
+      <c r="C49" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="B50" t="s">
         <v>231</v>
       </c>
-      <c r="C50" s="20">
+      <c r="C50" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="B51" s="15" t="s">
+      <c r="B51" t="s">
         <v>233</v>
       </c>
-      <c r="C51" s="20">
+      <c r="C51" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B52" s="15" t="s">
+      <c r="B52" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="20">
+      <c r="C52" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="B53" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="20">
+      <c r="C53" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="18" t="s">
+      <c r="A54" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="C54" s="20">
+      <c r="C54" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="B55" s="15" t="s">
+      <c r="B55" t="s">
         <v>167</v>
       </c>
-      <c r="C55" s="20">
+      <c r="C55" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B56" s="15" t="s">
+      <c r="B56" t="s">
         <v>169</v>
       </c>
-      <c r="C56" s="20">
+      <c r="C56" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" t="s">
         <v>171</v>
       </c>
-      <c r="C57" s="20">
+      <c r="C57" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" t="s">
         <v>173</v>
       </c>
-      <c r="C58" s="20">
+      <c r="C58" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B59" t="s">
         <v>175</v>
       </c>
-      <c r="C59" s="20">
+      <c r="C59" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B60" s="15" t="s">
+      <c r="B60" t="s">
         <v>177</v>
       </c>
-      <c r="C60" s="20">
+      <c r="C60" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="17" t="s">
+      <c r="A61" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" t="s">
         <v>179</v>
       </c>
-      <c r="C61" s="20">
+      <c r="C61" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="B62" s="15" t="s">
+      <c r="B62" t="s">
         <v>181</v>
       </c>
-      <c r="C62" s="20">
+      <c r="C62" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="17" t="s">
+      <c r="A63" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" t="s">
         <v>183</v>
       </c>
-      <c r="C63" s="20">
+      <c r="C63" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="17" t="s">
+      <c r="A64" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="B64" s="15" t="s">
+      <c r="B64" t="s">
         <v>185</v>
       </c>
-      <c r="C64" s="20">
+      <c r="C64" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="17" t="s">
+      <c r="A65" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" t="s">
         <v>18</v>
       </c>
-      <c r="C65" s="20">
+      <c r="C65" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="15" t="s">
+      <c r="A66" t="s">
         <v>23</v>
       </c>
-      <c r="B66" s="15" t="s">
+      <c r="B66" t="s">
         <v>49</v>
       </c>
-      <c r="C66" s="20">
+      <c r="C66" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="17" t="s">
+      <c r="A67" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B67" s="15" t="s">
+      <c r="B67" t="s">
         <v>56</v>
       </c>
-      <c r="C67" s="21">
+      <c r="C67" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="17" t="s">
+      <c r="A68" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" t="s">
         <v>58</v>
       </c>
-      <c r="C68" s="21">
+      <c r="C68" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="17" t="s">
+      <c r="A69" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="15" t="s">
+      <c r="B69" t="s">
         <v>60</v>
       </c>
-      <c r="C69" s="21">
+      <c r="C69" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="17" t="s">
+      <c r="A70" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B70" s="15" t="s">
+      <c r="B70" t="s">
         <v>62</v>
       </c>
-      <c r="C70" s="21">
+      <c r="C70" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="17" t="s">
+      <c r="A71" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="15" t="s">
+      <c r="B71" t="s">
         <v>64</v>
       </c>
-      <c r="C71" s="21">
+      <c r="C71" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="17" t="s">
+      <c r="A72" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B72" s="15" t="s">
+      <c r="B72" t="s">
         <v>66</v>
       </c>
-      <c r="C72" s="21">
+      <c r="C72" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="17" t="s">
+      <c r="A73" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B73" s="15" t="s">
+      <c r="B73" t="s">
         <v>68</v>
       </c>
-      <c r="C73" s="21">
+      <c r="C73" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="17" t="s">
+      <c r="A74" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B74" s="15" t="s">
+      <c r="B74" t="s">
         <v>70</v>
       </c>
-      <c r="C74" s="21">
+      <c r="C74" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="17" t="s">
+      <c r="A75" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B75" s="15" t="s">
+      <c r="B75" t="s">
         <v>72</v>
       </c>
-      <c r="C75" s="21">
+      <c r="C75" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="17" t="s">
+      <c r="A76" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="B76" s="15" t="s">
+      <c r="B76" t="s">
         <v>74</v>
       </c>
-      <c r="C76" s="21">
+      <c r="C76" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="17" t="s">
+      <c r="A77" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B77" s="15" t="s">
+      <c r="B77" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="21">
+      <c r="C77" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="17" t="s">
+      <c r="A78" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B78" s="15" t="s">
+      <c r="B78" t="s">
         <v>78</v>
       </c>
-      <c r="C78" s="21">
+      <c r="C78" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="17" t="s">
+      <c r="A79" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="15" t="s">
+      <c r="B79" t="s">
         <v>80</v>
       </c>
-      <c r="C79" s="21">
+      <c r="C79" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="17" t="s">
+      <c r="A80" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B80" s="15" t="s">
+      <c r="B80" t="s">
         <v>82</v>
       </c>
-      <c r="C80" s="21">
+      <c r="C80" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="17" t="s">
+      <c r="A81" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="15" t="s">
+      <c r="B81" t="s">
         <v>84</v>
       </c>
-      <c r="C81" s="21">
+      <c r="C81" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="17" t="s">
+      <c r="A82" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B82" s="15" t="s">
+      <c r="B82" t="s">
         <v>86</v>
       </c>
-      <c r="C82" s="21">
+      <c r="C82" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="17" t="s">
+      <c r="A83" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B83" s="15" t="s">
+      <c r="B83" t="s">
         <v>88</v>
       </c>
-      <c r="C83" s="21">
+      <c r="C83" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="17" t="s">
+      <c r="A84" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B84" s="15" t="s">
+      <c r="B84" t="s">
         <v>90</v>
       </c>
-      <c r="C84" s="21">
+      <c r="C84" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="17" t="s">
+      <c r="A85" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="B85" s="15" t="s">
+      <c r="B85" t="s">
         <v>253</v>
       </c>
-      <c r="C85" s="20">
+      <c r="C85" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="17" t="s">
+      <c r="A86" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="B86" s="15" t="s">
+      <c r="B86" t="s">
         <v>251</v>
       </c>
-      <c r="C86" s="20">
+      <c r="C86" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="17" t="s">
+      <c r="A87" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B87" s="15" t="s">
+      <c r="B87" t="s">
         <v>16</v>
       </c>
-      <c r="C87" s="20">
+      <c r="C87" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="17" t="s">
+      <c r="A88" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B88" s="15" t="s">
+      <c r="B88" t="s">
         <v>19</v>
       </c>
-      <c r="C88" s="20">
+      <c r="C88" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="17" t="s">
+      <c r="A89" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="B89" s="15" t="s">
+      <c r="B89" t="s">
         <v>255</v>
       </c>
-      <c r="C89" s="20">
+      <c r="C89" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="17" t="s">
+      <c r="A90" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="B90" s="15" t="s">
+      <c r="B90" t="s">
         <v>235</v>
       </c>
-      <c r="C90" s="20">
+      <c r="C90" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="17" t="s">
+      <c r="A91" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="B91" s="15" t="s">
+      <c r="B91" t="s">
         <v>237</v>
       </c>
-      <c r="C91" s="20">
+      <c r="C91" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="17" t="s">
+      <c r="A92" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="B92" s="15" t="s">
+      <c r="B92" t="s">
         <v>239</v>
       </c>
-      <c r="C92" s="20">
+      <c r="C92" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="17" t="s">
+      <c r="A93" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="B93" s="15" t="s">
+      <c r="B93" t="s">
         <v>241</v>
       </c>
-      <c r="C93" s="20">
+      <c r="C93" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="17" t="s">
+      <c r="A94" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="B94" s="15" t="s">
+      <c r="B94" t="s">
         <v>243</v>
       </c>
-      <c r="C94" s="20">
+      <c r="C94" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="17" t="s">
+      <c r="A95" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="B95" s="15" t="s">
+      <c r="B95" t="s">
         <v>245</v>
       </c>
-      <c r="C95" s="20">
+      <c r="C95" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="17" t="s">
+      <c r="A96" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="B96" s="15" t="s">
+      <c r="B96" t="s">
         <v>247</v>
       </c>
-      <c r="C96" s="20">
+      <c r="C96" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="17" t="s">
+      <c r="A97" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="B97" s="15" t="s">
+      <c r="B97" t="s">
         <v>249</v>
       </c>
-      <c r="C97" s="20">
+      <c r="C97" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="15" t="s">
+      <c r="A98" t="s">
         <v>21</v>
       </c>
-      <c r="B98" s="15" t="s">
+      <c r="B98" t="s">
         <v>52</v>
       </c>
-      <c r="C98" s="20">
+      <c r="C98" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="15" t="s">
+      <c r="A99" t="s">
         <v>29</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" t="s">
         <v>51</v>
       </c>
-      <c r="C99" s="20">
+      <c r="C99" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="15" t="s">
+      <c r="A100" t="s">
         <v>28</v>
       </c>
-      <c r="B100" s="15" t="s">
+      <c r="B100" t="s">
         <v>50</v>
       </c>
-      <c r="C100" s="20">
+      <c r="C100" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="17" t="s">
+      <c r="A101" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B101" s="15" t="s">
+      <c r="B101" t="s">
         <v>20</v>
       </c>
-      <c r="C101" s="20">
+      <c r="C101" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="17" t="s">
+      <c r="A102" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B102" s="15" t="s">
+      <c r="B102" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="20">
+      <c r="C102" s="15">
         <v>2</v>
       </c>
       <c r="D102" s="10" t="s">
@@ -3105,123 +3116,123 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="17" t="s">
+      <c r="A103" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B103" s="15" t="s">
+      <c r="B103" t="s">
         <v>103</v>
       </c>
-      <c r="C103" s="20">
+      <c r="C103" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="17" t="s">
+      <c r="A104" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B104" s="15" t="s">
+      <c r="B104" t="s">
         <v>105</v>
       </c>
-      <c r="C104" s="20">
+      <c r="C104" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="17" t="s">
+      <c r="A105" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B105" s="15" t="s">
+      <c r="B105" t="s">
         <v>107</v>
       </c>
-      <c r="C105" s="20">
+      <c r="C105" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="17" t="s">
+      <c r="A106" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B106" s="15" t="s">
+      <c r="B106" t="s">
         <v>109</v>
       </c>
-      <c r="C106" s="20">
+      <c r="C106" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="17" t="s">
+      <c r="A107" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B107" s="15" t="s">
+      <c r="B107" t="s">
         <v>111</v>
       </c>
-      <c r="C107" s="20">
+      <c r="C107" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="17" t="s">
+      <c r="A108" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B108" s="15" t="s">
+      <c r="B108" t="s">
         <v>113</v>
       </c>
-      <c r="C108" s="20">
+      <c r="C108" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="17" t="s">
+      <c r="A109" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B109" s="15" t="s">
+      <c r="B109" t="s">
         <v>115</v>
       </c>
-      <c r="C109" s="20">
+      <c r="C109" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="17" t="s">
+      <c r="A110" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B110" s="15" t="s">
+      <c r="B110" t="s">
         <v>117</v>
       </c>
-      <c r="C110" s="20">
+      <c r="C110" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="17" t="s">
+      <c r="A111" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B111" s="15" t="s">
+      <c r="B111" t="s">
         <v>119</v>
       </c>
-      <c r="C111" s="20">
+      <c r="C111" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="17" t="s">
+      <c r="A112" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="B112" s="15" t="s">
+      <c r="B112" t="s">
         <v>257</v>
       </c>
-      <c r="C112" s="20" t="s">
+      <c r="C112" s="15" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="17" t="s">
+      <c r="A113" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="B113" s="15" t="s">
+      <c r="B113" t="s">
         <v>259</v>
       </c>
-      <c r="C113" s="20">
+      <c r="C113" s="15">
         <v>1</v>
       </c>
     </row>

--- a/static_files/manual.xlsx
+++ b/static_files/manual.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KEC\HL7-Helper\static_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAC81C1-FD59-446A-AC65-48D2E46CB81C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B24BC7A-C7BB-4184-A824-55AA37D65D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{ED8BEDC3-DBCC-4188-B4B2-8E63CDEE6B29}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{ED8BEDC3-DBCC-4188-B4B2-8E63CDEE6B29}"/>
   </bookViews>
   <sheets>
     <sheet name="Uebersicht" sheetId="3" r:id="rId1"/>
-    <sheet name="Abteilungsmapping" sheetId="14" r:id="rId2"/>
+    <sheet name="Besonderheiten" sheetId="15" r:id="rId2"/>
+    <sheet name="Abteilungsmapping" sheetId="14" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="266">
   <si>
     <t>Diacos</t>
   </si>
@@ -888,6 +889,12 @@
   </si>
   <si>
     <t>Todos</t>
+  </si>
+  <si>
+    <t>Bei stationären wie auch ambulanten Patienten wird in der Regel immer der Besucher (Stammdaten des Patienten), sowie auch der Besuch (mit Gültigkeitsdauer, Zimmer, Bett, Zutrittsrechten etc.) angelegt</t>
+  </si>
+  <si>
+    <t>Allerdings gibt es in Interflex eine Logik, dass bei ambulanten Fällen der Besuch nur angelegt wird, wenn die Abteilung in Interflex unter ambulante Fälle erfasst ist</t>
   </si>
 </sst>
 </file>
@@ -1056,11 +1063,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1077,6 +1084,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>572750</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>29229</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Grafik 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1D39634-A3B3-4345-8264-166BFB61CFD0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="676275"/>
+          <a:ext cx="8954750" cy="4686954"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1558,7 +1614,7 @@
       <c r="F8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="16" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1654,6 +1710,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D5730A0-3A53-4D53-92F5-8CCFD01C3540}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66F66978-979D-4700-BBDA-412E99A414BB}">
   <dimension ref="A1:Q113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1674,20 +1756,20 @@
       <c r="C1" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -1699,18 +1781,18 @@
       <c r="C2" s="15">
         <v>1</v>
       </c>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
@@ -1722,18 +1804,18 @@
       <c r="C3" s="15">
         <v>1</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -1745,18 +1827,18 @@
       <c r="C4" s="15">
         <v>2</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -1768,18 +1850,18 @@
       <c r="C5" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
@@ -1791,18 +1873,18 @@
       <c r="C6" s="15">
         <v>2</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
@@ -1814,18 +1896,18 @@
       <c r="C7" s="15">
         <v>2</v>
       </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -1837,18 +1919,18 @@
       <c r="C8" s="15">
         <v>2</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
@@ -1860,18 +1942,18 @@
       <c r="C9" s="15">
         <v>2</v>
       </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
@@ -1883,18 +1965,18 @@
       <c r="C10" s="15">
         <v>2</v>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
@@ -1906,18 +1988,18 @@
       <c r="C11" s="15">
         <v>2</v>
       </c>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
@@ -1929,18 +2011,18 @@
       <c r="C12" s="15">
         <v>2</v>
       </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
@@ -1952,18 +2034,18 @@
       <c r="C13" s="15">
         <v>2</v>
       </c>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
@@ -1975,18 +2057,18 @@
       <c r="C14" s="15">
         <v>2</v>
       </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
@@ -1998,18 +2080,18 @@
       <c r="C15" s="15">
         <v>2</v>
       </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
@@ -2021,18 +2103,18 @@
       <c r="C16" s="15">
         <v>2</v>
       </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
@@ -2044,18 +2126,18 @@
       <c r="C17" s="15">
         <v>2</v>
       </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
@@ -2067,18 +2149,18 @@
       <c r="C18" s="15">
         <v>2</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
@@ -2090,18 +2172,18 @@
       <c r="C19" s="15">
         <v>2</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
@@ -2113,18 +2195,18 @@
       <c r="C20" s="15">
         <v>2</v>
       </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
@@ -2136,18 +2218,18 @@
       <c r="C21" s="15">
         <v>2</v>
       </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -2159,18 +2241,18 @@
       <c r="C22" s="15">
         <v>2</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
@@ -2182,18 +2264,18 @@
       <c r="C23" s="15">
         <v>2</v>
       </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -2205,18 +2287,18 @@
       <c r="C24" s="15">
         <v>2</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
@@ -2228,18 +2310,18 @@
       <c r="C25" s="15">
         <v>2</v>
       </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
@@ -2251,18 +2333,18 @@
       <c r="C26" s="15">
         <v>2</v>
       </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
@@ -2274,18 +2356,18 @@
       <c r="C27" s="15">
         <v>2</v>
       </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">

--- a/static_files/manual.xlsx
+++ b/static_files/manual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KEC\HL7-Helper\static_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B24BC7A-C7BB-4184-A824-55AA37D65D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0517608-B623-4FC9-B47B-6EB09D9F994B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{ED8BEDC3-DBCC-4188-B4B2-8E63CDEE6B29}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{ED8BEDC3-DBCC-4188-B4B2-8E63CDEE6B29}"/>
   </bookViews>
   <sheets>
     <sheet name="Uebersicht" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="276">
   <si>
     <t>Diacos</t>
   </si>
@@ -896,12 +896,42 @@
   <si>
     <t>Allerdings gibt es in Interflex eine Logik, dass bei ambulanten Fällen der Besuch nur angelegt wird, wenn die Abteilung in Interflex unter ambulante Fälle erfasst ist</t>
   </si>
+  <si>
+    <t>IF 6040</t>
+  </si>
+  <si>
+    <t>CDMS</t>
+  </si>
+  <si>
+    <t>IBIcare</t>
+  </si>
+  <si>
+    <t>IBI-care - Reha Bellikon TEST</t>
+  </si>
+  <si>
+    <t>RKB i-engine</t>
+  </si>
+  <si>
+    <t>Ablage Testsystem</t>
+  </si>
+  <si>
+    <t>\\rehabellikon.ch\dfs\CDMS_TEST_TRANSFER</t>
+  </si>
+  <si>
+    <t>URL Prod</t>
+  </si>
+  <si>
+    <t>URL Test</t>
+  </si>
+  <si>
+    <t>von CDMS Server starten</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -993,8 +1023,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1004,6 +1042,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1017,10 +1061,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1066,11 +1111,15 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1092,13 +1141,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>572750</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>287000</xdr:colOff>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>29229</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1711,27 +1760,124 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D5730A0-3A53-4D53-92F5-8CCFD01C3540}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>265</v>
       </c>
     </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>273</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>274</v>
+      </c>
+      <c r="B34" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>271</v>
+      </c>
+      <c r="B35" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="20"/>
+      <c r="N38" s="20"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>274</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>269</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://interflex.rehabellikon.ch/IF6040/IFWebLogin.aspx?ReturnUrl=%2fIF6040%2fWelcome.aspx" xr:uid="{5EAB0F4D-07C8-4F6D-8B6A-5CE2918C4C42}"/>
+    <hyperlink ref="B39" r:id="rId2" display="https://ibi-care-test.rehabellikon.ch/IBI-care/login?notAuthenticated=true&amp;returnUrl=%2F" xr:uid="{4A1346EA-37CD-4A4D-9CA2-05582C8B6E97}"/>
+    <hyperlink ref="B33" r:id="rId3" display="https://cdmsprod.rehabellikon.ch/auth-service/authenticate/start?spnego=failed&amp;application=tsclient&amp;path=%23/main" xr:uid="{124664E6-8F04-4B4A-A41F-DB3D29598C28}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -1756,20 +1902,20 @@
       <c r="C1" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -1781,18 +1927,18 @@
       <c r="C2" s="15">
         <v>1</v>
       </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
@@ -1804,18 +1950,18 @@
       <c r="C3" s="15">
         <v>1</v>
       </c>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -1827,18 +1973,18 @@
       <c r="C4" s="15">
         <v>2</v>
       </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -1850,18 +1996,18 @@
       <c r="C5" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
@@ -1873,18 +2019,18 @@
       <c r="C6" s="15">
         <v>2</v>
       </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
@@ -1896,18 +2042,18 @@
       <c r="C7" s="15">
         <v>2</v>
       </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -1919,18 +2065,18 @@
       <c r="C8" s="15">
         <v>2</v>
       </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
@@ -1942,18 +2088,18 @@
       <c r="C9" s="15">
         <v>2</v>
       </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
@@ -1965,18 +2111,18 @@
       <c r="C10" s="15">
         <v>2</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
@@ -1988,18 +2134,18 @@
       <c r="C11" s="15">
         <v>2</v>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
@@ -2011,18 +2157,18 @@
       <c r="C12" s="15">
         <v>2</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
@@ -2034,18 +2180,18 @@
       <c r="C13" s="15">
         <v>2</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
@@ -2057,18 +2203,18 @@
       <c r="C14" s="15">
         <v>2</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
@@ -2080,18 +2226,18 @@
       <c r="C15" s="15">
         <v>2</v>
       </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
@@ -2103,18 +2249,18 @@
       <c r="C16" s="15">
         <v>2</v>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
@@ -2126,18 +2272,18 @@
       <c r="C17" s="15">
         <v>2</v>
       </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
@@ -2149,18 +2295,18 @@
       <c r="C18" s="15">
         <v>2</v>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
@@ -2172,18 +2318,18 @@
       <c r="C19" s="15">
         <v>2</v>
       </c>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
@@ -2195,18 +2341,18 @@
       <c r="C20" s="15">
         <v>2</v>
       </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
@@ -2218,18 +2364,18 @@
       <c r="C21" s="15">
         <v>2</v>
       </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -2241,18 +2387,18 @@
       <c r="C22" s="15">
         <v>2</v>
       </c>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
@@ -2264,18 +2410,18 @@
       <c r="C23" s="15">
         <v>2</v>
       </c>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
@@ -2287,18 +2433,18 @@
       <c r="C24" s="15">
         <v>2</v>
       </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
@@ -2310,18 +2456,18 @@
       <c r="C25" s="15">
         <v>2</v>
       </c>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
@@ -2333,18 +2479,18 @@
       <c r="C26" s="15">
         <v>2</v>
       </c>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
@@ -2356,18 +2502,18 @@
       <c r="C27" s="15">
         <v>2</v>
       </c>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">

--- a/static_files/manual.xlsx
+++ b/static_files/manual.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KEC\HL7-Helper\static_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0517608-B623-4FC9-B47B-6EB09D9F994B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E40887-A033-4BF9-9983-B87CC2C7B548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{ED8BEDC3-DBCC-4188-B4B2-8E63CDEE6B29}"/>
   </bookViews>
   <sheets>
     <sheet name="Uebersicht" sheetId="3" r:id="rId1"/>
-    <sheet name="Besonderheiten" sheetId="15" r:id="rId2"/>
+    <sheet name="Eventcodes" sheetId="16" r:id="rId2"/>
     <sheet name="Abteilungsmapping" sheetId="14" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="314">
   <si>
     <t>Diacos</t>
   </si>
@@ -79,42 +79,6 @@
     <t>EKG</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Technischer Test OK </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">(das einzige was nicht nach Diacos übernommen wird, obwohl es offenbar korrekt aus Orchestra gesendet wird ist der Fallstatus stationär/ambulant. In Diacos wird immer stationär angezeigt, siehe Details im Sheet DIACOS) --&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Fachtest durchführen</t>
-    </r>
-  </si>
-  <si>
-    <t>Technischer Test OK, Interflex scheint aber ambulante Fälle zu ignorieren</t>
-  </si>
-  <si>
     <t>Technischer Test OK</t>
   </si>
   <si>
@@ -175,49 +139,19 @@
     <t>Daten</t>
   </si>
   <si>
-    <t>Fachverantwortliche/r</t>
-  </si>
-  <si>
-    <t>Testsystem vorhanden</t>
-  </si>
-  <si>
     <t>Nein</t>
   </si>
   <si>
     <t>Ja</t>
   </si>
   <si>
-    <t>Franziska Zayakio</t>
-  </si>
-  <si>
-    <t>Ann-Sophie Ingelin</t>
-  </si>
-  <si>
-    <t>Paolo Aceto</t>
-  </si>
-  <si>
-    <t>Adrian Mieth</t>
-  </si>
-  <si>
-    <t>Marcel Hagenbuch</t>
-  </si>
-  <si>
     <t>Anassung wegen neuen SAP OE notwendig</t>
   </si>
   <si>
     <t>Erst testbar, wenn Ines Patfall funktioniert</t>
   </si>
   <si>
-    <t>Was ist das für ein Fileformat, komme nicht mit admkeu auf server?</t>
-  </si>
-  <si>
-    <t>Wo Testfiles ablegen, es gibt ar keine AD-Gruppe für Zugriff auf Linuxfileserver CDMS testsystem</t>
-  </si>
-  <si>
     <t>Check&amp;Act TCG</t>
-  </si>
-  <si>
-    <t>-&gt; neue ambulante Abteilungen in Interflex ergänzen</t>
   </si>
   <si>
     <t>F_NEUROP</t>
@@ -926,12 +860,162 @@
   <si>
     <t>von CDMS Server starten</t>
   </si>
+  <si>
+    <t>Event Code</t>
+  </si>
+  <si>
+    <t>Bedeutung</t>
+  </si>
+  <si>
+    <t>Typischer Usecase</t>
+  </si>
+  <si>
+    <t>A01</t>
+  </si>
+  <si>
+    <t>Admission / Visit Notification</t>
+  </si>
+  <si>
+    <t>Stationäre Aufnahme eines Patienten</t>
+  </si>
+  <si>
+    <t>A02</t>
+  </si>
+  <si>
+    <t>Transfer a Patient</t>
+  </si>
+  <si>
+    <t>Verlegung (z. B. Betten-/Stationenwechsel)</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>Discharge / End Visit</t>
+  </si>
+  <si>
+    <t>Entlassung des Patienten</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>Register a Patient</t>
+  </si>
+  <si>
+    <t>Ambulante Registrierung / Notfall-Aufnahme</t>
+  </si>
+  <si>
+    <t>A08</t>
+  </si>
+  <si>
+    <t>Update Patient Information</t>
+  </si>
+  <si>
+    <t>Änderung von Stammdaten oder Falldaten</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>Cancel Admission</t>
+  </si>
+  <si>
+    <t>Stornierung einer Aufnahme (A01/A04)</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>Cancel Transfer</t>
+  </si>
+  <si>
+    <t>Stornierung einer Verlegung</t>
+  </si>
+  <si>
+    <t>A13</t>
+  </si>
+  <si>
+    <t>Cancel Discharge</t>
+  </si>
+  <si>
+    <t>Stornierung einer Entlassung</t>
+  </si>
+  <si>
+    <t>A31</t>
+  </si>
+  <si>
+    <t>Update Person Information</t>
+  </si>
+  <si>
+    <t>Reine Personen-Stammdatenänderung (ohne Fallbezug)</t>
+  </si>
+  <si>
+    <t>A40</t>
+  </si>
+  <si>
+    <t>Merge Patient - Patient ID</t>
+  </si>
+  <si>
+    <t>Zusammenführung von zwei Patientenakten (Dublettenbereinigung)</t>
+  </si>
+  <si>
+    <t>A14</t>
+  </si>
+  <si>
+    <t>Pending Admit</t>
+  </si>
+  <si>
+    <t>Geplante / Ausstehende Aufnahme)</t>
+  </si>
+  <si>
+    <t>Fachlicher Test OK</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Auf Paolo warten</t>
+  </si>
+  <si>
+    <t>(x)</t>
+  </si>
+  <si>
+    <t>Interflex prüft bei ambulanten Fällen, ob die Abteilung in Interflex hinterlegt ist</t>
+  </si>
+  <si>
+    <t>Zugriff auf CDMS-Filesystem nun gegeben</t>
+  </si>
+  <si>
+    <t>ID-Diacos-Absprung</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>Pre-Admit a Patient</t>
+  </si>
+  <si>
+    <t>Voraufnahme / Präregistrierung eines Patienten</t>
+  </si>
+  <si>
+    <t>A28</t>
+  </si>
+  <si>
+    <t>Add Person Information</t>
+  </si>
+  <si>
+    <t>Personenstammdaten anlegen</t>
+  </si>
+  <si>
+    <t>Technischer Test OK (das einzige was nicht nach Diacos übernommen wird, obwohl es offenbar korrekt aus Orchestra gesendet wird ist der Fallstatus stationär/ambulant. In Diacos wird immer stationär angezeigt.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -942,13 +1026,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF7030A0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -977,21 +1054,6 @@
     <font>
       <sz val="11"/>
       <color theme="4"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="4"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="9"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1031,6 +1093,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1052,7 +1127,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1060,69 +1135,99 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1137,25 +1242,20 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>287000</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>29229</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="8954750" cy="4686954"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Grafik 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1D39634-A3B3-4345-8264-166BFB61CFD0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{535866BC-70CD-4887-855F-DBD5AE265FE0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1171,7 +1271,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="676275"/>
+          <a:off x="0" y="866775"/>
           <a:ext cx="8954750" cy="4686954"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1180,7 +1280,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1501,39 +1601,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B86EEF-BB3A-440C-B306-C644435507BF}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="69.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="62" style="2" customWidth="1"/>
     <col min="6" max="6" width="39.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>263</v>
+      <c r="G1" s="4" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -1543,17 +1643,14 @@
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>36</v>
+      <c r="C2" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1563,15 +1660,15 @@
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="6"/>
+      <c r="C3" s="2" t="s">
+        <v>301</v>
+      </c>
       <c r="D3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>36</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1581,14 +1678,12 @@
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="C4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E4" s="3"/>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1598,15 +1693,12 @@
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>37</v>
+      <c r="C5" s="2"/>
+      <c r="E5" s="3" t="s">
+        <v>302</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1616,15 +1708,10 @@
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="E6" s="3"/>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1634,54 +1721,48 @@
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="C7" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E7" s="3"/>
       <c r="F7" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>36</v>
+      <c r="C8" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="G8" s="13"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>37</v>
+      <c r="C9" s="2"/>
+      <c r="E9" s="3" t="s">
+        <v>305</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1691,11 +1772,10 @@
       <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="E10" s="3"/>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1705,14 +1785,12 @@
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>37</v>
+      <c r="C11" s="2"/>
+      <c r="E11" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1722,162 +1800,966 @@
       <c r="B12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="E12" s="3"/>
       <c r="F12" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="E13" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="E13" s="3"/>
       <c r="F13" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E14" s="9"/>
+      <c r="A14" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E15" s="9"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>261</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>252</v>
+      </c>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>253</v>
+      </c>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+      <c r="K32"/>
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33"/>
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34"/>
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35"/>
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37"/>
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38"/>
+      <c r="B38"/>
+      <c r="C38"/>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="J38"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39"/>
+      <c r="B39"/>
+      <c r="C39"/>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39"/>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40"/>
+      <c r="B40"/>
+      <c r="C40"/>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44"/>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44"/>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45"/>
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45"/>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46"/>
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47"/>
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47"/>
+      <c r="K47"/>
+      <c r="L47"/>
+      <c r="M47"/>
+      <c r="N47"/>
+      <c r="O47"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>261</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49"/>
+      <c r="K49"/>
+      <c r="L49"/>
+      <c r="M49"/>
+      <c r="N49"/>
+      <c r="O49"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>262</v>
+      </c>
+      <c r="B50" t="s">
+        <v>263</v>
+      </c>
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50"/>
+      <c r="K50"/>
+      <c r="L50"/>
+      <c r="M50"/>
+      <c r="N50"/>
+      <c r="O50"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>259</v>
+      </c>
+      <c r="B51" t="s">
+        <v>260</v>
+      </c>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51"/>
+      <c r="K51"/>
+      <c r="L51"/>
+      <c r="M51"/>
+      <c r="N51"/>
+      <c r="O51"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52"/>
+      <c r="B52"/>
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+      <c r="M52"/>
+      <c r="N52"/>
+      <c r="O52"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53"/>
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
+      <c r="M53"/>
+      <c r="N53"/>
+      <c r="O53"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="16"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
+      <c r="N54" s="16"/>
+      <c r="O54"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>262</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
+      <c r="I55"/>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+      <c r="M55"/>
+      <c r="N55"/>
+      <c r="O55"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56"/>
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+      <c r="M56"/>
+      <c r="N56"/>
+      <c r="O56"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57"/>
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+      <c r="M57"/>
+      <c r="N57"/>
+      <c r="O57"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58"/>
+      <c r="B58"/>
+      <c r="C58"/>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58"/>
+      <c r="G58"/>
+      <c r="H58"/>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
+      <c r="L58"/>
+      <c r="M58"/>
+      <c r="N58"/>
+      <c r="O58"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:B14">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$D2="x"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>$C2="x"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="B18" r:id="rId1" display="https://interflex.rehabellikon.ch/IF6040/IFWebLogin.aspx?ReturnUrl=%2fIF6040%2fWelcome.aspx" xr:uid="{5EAB0F4D-07C8-4F6D-8B6A-5CE2918C4C42}"/>
+    <hyperlink ref="B55" r:id="rId2" display="https://ibi-care-test.rehabellikon.ch/IBI-care/login?notAuthenticated=true&amp;returnUrl=%2F" xr:uid="{4A1346EA-37CD-4A4D-9CA2-05582C8B6E97}"/>
+    <hyperlink ref="B49" r:id="rId3" display="https://cdmsprod.rehabellikon.ch/auth-service/authenticate/start?spnego=failed&amp;application=tsclient&amp;path=%23/main" xr:uid="{124664E6-8F04-4B4A-A41F-DB3D29598C28}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D5730A0-3A53-4D53-92F5-8CCFD01C3540}">
-  <dimension ref="A1:N39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCEF7D4B-9D7B-400C-B211-2249CA61375D}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="37.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.140625" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
+    <col min="3" max="4" width="39.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="B2" s="17" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>273</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B4" s="18" t="s">
         <v>274</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C4" s="18" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>271</v>
-      </c>
-      <c r="B35" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="20"/>
-      <c r="N38" s="20"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>274</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>269</v>
+    <row r="5" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://interflex.rehabellikon.ch/IF6040/IFWebLogin.aspx?ReturnUrl=%2fIF6040%2fWelcome.aspx" xr:uid="{5EAB0F4D-07C8-4F6D-8B6A-5CE2918C4C42}"/>
-    <hyperlink ref="B39" r:id="rId2" display="https://ibi-care-test.rehabellikon.ch/IBI-care/login?notAuthenticated=true&amp;returnUrl=%2F" xr:uid="{4A1346EA-37CD-4A4D-9CA2-05582C8B6E97}"/>
-    <hyperlink ref="B33" r:id="rId3" display="https://cdmsprod.rehabellikon.ch/auth-service/authenticate/start?spnego=failed&amp;application=tsclient&amp;path=%23/main" xr:uid="{124664E6-8F04-4B4A-A41F-DB3D29598C28}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -1888,1579 +2770,1579 @@
   <cols>
     <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" style="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="A1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>91</v>
+      <c r="A2" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C2" s="15">
+        <v>80</v>
+      </c>
+      <c r="C2" s="12">
         <v>1</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>93</v>
+      <c r="A3" s="9" t="s">
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="15">
+        <v>82</v>
+      </c>
+      <c r="C3" s="12">
         <v>1</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>95</v>
+      <c r="A4" s="9" t="s">
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="15">
-        <v>2</v>
-      </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
+        <v>84</v>
+      </c>
+      <c r="C4" s="12">
+        <v>2</v>
+      </c>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="12">
+        <v>2</v>
+      </c>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="12">
+        <v>2</v>
+      </c>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="12">
+        <v>2</v>
+      </c>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="12">
+        <v>2</v>
+      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="12">
+        <v>2</v>
+      </c>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B11" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="C11" s="12">
+        <v>2</v>
+      </c>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B12" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="15">
-        <v>2</v>
-      </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="C12" s="12">
+        <v>2</v>
+      </c>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B13" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="15">
-        <v>2</v>
-      </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="C13" s="12">
+        <v>2</v>
+      </c>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B14" t="s">
         <v>127</v>
       </c>
-      <c r="C8" s="15">
-        <v>2</v>
-      </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="C14" s="12">
+        <v>2</v>
+      </c>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B15" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="15">
-        <v>2</v>
-      </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="C15" s="12">
+        <v>2</v>
+      </c>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B16" t="s">
         <v>131</v>
       </c>
-      <c r="C10" s="15">
-        <v>2</v>
-      </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="C16" s="12">
+        <v>2</v>
+      </c>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B17" t="s">
         <v>133</v>
       </c>
-      <c r="C11" s="15">
-        <v>2</v>
-      </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="C17" s="12">
+        <v>2</v>
+      </c>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B18" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="15">
-        <v>2</v>
-      </c>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="C18" s="12">
+        <v>2</v>
+      </c>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B19" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="15">
-        <v>2</v>
-      </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="C19" s="12">
+        <v>2</v>
+      </c>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B20" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="15">
-        <v>2</v>
-      </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="C20" s="12">
+        <v>2</v>
+      </c>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B21" t="s">
         <v>141</v>
       </c>
-      <c r="C15" s="15">
-        <v>2</v>
-      </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="C21" s="12">
+        <v>2</v>
+      </c>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B22" t="s">
         <v>143</v>
       </c>
-      <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="C22" s="12">
+        <v>2</v>
+      </c>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B23" t="s">
         <v>145</v>
       </c>
-      <c r="C17" s="15">
-        <v>2</v>
-      </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="C23" s="12">
+        <v>2</v>
+      </c>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B24" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="15">
-        <v>2</v>
-      </c>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="C24" s="12">
+        <v>2</v>
+      </c>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B25" t="s">
         <v>149</v>
       </c>
-      <c r="C19" s="15">
-        <v>2</v>
-      </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="C25" s="12">
+        <v>2</v>
+      </c>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B26" t="s">
         <v>151</v>
       </c>
-      <c r="C20" s="15">
-        <v>2</v>
-      </c>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="C26" s="12">
+        <v>2</v>
+      </c>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B27" t="s">
         <v>153</v>
       </c>
-      <c r="C21" s="15">
-        <v>2</v>
-      </c>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="C27" s="12">
+        <v>2</v>
+      </c>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28" t="s">
+        <v>175</v>
+      </c>
+      <c r="C28" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29" t="s">
+        <v>177</v>
+      </c>
+      <c r="C29" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B30" t="s">
+        <v>179</v>
+      </c>
+      <c r="C30" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B31" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C32" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B33" t="s">
+        <v>185</v>
+      </c>
+      <c r="C33" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B34" t="s">
+        <v>187</v>
+      </c>
+      <c r="C34" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B35" t="s">
+        <v>189</v>
+      </c>
+      <c r="C35" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B36" t="s">
+        <v>191</v>
+      </c>
+      <c r="C36" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B37" t="s">
+        <v>193</v>
+      </c>
+      <c r="C37" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B39" t="s">
+        <v>197</v>
+      </c>
+      <c r="C39" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B40" t="s">
+        <v>199</v>
+      </c>
+      <c r="C40" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B41" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B42" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B43" t="s">
+        <v>205</v>
+      </c>
+      <c r="C43" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B44" t="s">
+        <v>207</v>
+      </c>
+      <c r="C44" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B45" t="s">
+        <v>209</v>
+      </c>
+      <c r="C45" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B46" t="s">
+        <v>211</v>
+      </c>
+      <c r="C46" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="B47" t="s">
+        <v>213</v>
+      </c>
+      <c r="C47" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" t="s">
+        <v>215</v>
+      </c>
+      <c r="C48" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B49" t="s">
+        <v>217</v>
+      </c>
+      <c r="C49" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B50" t="s">
+        <v>219</v>
+      </c>
+      <c r="C50" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B51" t="s">
+        <v>221</v>
+      </c>
+      <c r="C51" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B52" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B55" t="s">
         <v>155</v>
       </c>
-      <c r="C22" s="15">
-        <v>2</v>
-      </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="C55" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B56" t="s">
         <v>157</v>
       </c>
-      <c r="C23" s="15">
-        <v>2</v>
-      </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="C56" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B57" t="s">
         <v>159</v>
       </c>
-      <c r="C24" s="15">
-        <v>2</v>
-      </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+      <c r="C57" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B58" t="s">
         <v>161</v>
       </c>
-      <c r="C25" s="15">
-        <v>2</v>
-      </c>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="C58" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B59" t="s">
         <v>163</v>
       </c>
-      <c r="C26" s="15">
-        <v>2</v>
-      </c>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+      <c r="C59" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B60" t="s">
         <v>165</v>
       </c>
-      <c r="C27" s="15">
-        <v>2</v>
-      </c>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="B28" t="s">
-        <v>187</v>
-      </c>
-      <c r="C28" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="B29" t="s">
-        <v>189</v>
-      </c>
-      <c r="C29" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="B30" t="s">
-        <v>191</v>
-      </c>
-      <c r="C30" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="B31" t="s">
-        <v>193</v>
-      </c>
-      <c r="C31" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="B32" t="s">
-        <v>195</v>
-      </c>
-      <c r="C32" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B33" t="s">
-        <v>197</v>
-      </c>
-      <c r="C33" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B34" t="s">
-        <v>199</v>
-      </c>
-      <c r="C34" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="B35" t="s">
-        <v>201</v>
-      </c>
-      <c r="C35" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="B36" t="s">
-        <v>203</v>
-      </c>
-      <c r="C36" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="B37" t="s">
-        <v>205</v>
-      </c>
-      <c r="C37" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="B38" t="s">
-        <v>207</v>
-      </c>
-      <c r="C38" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B39" t="s">
-        <v>209</v>
-      </c>
-      <c r="C39" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="B40" t="s">
-        <v>211</v>
-      </c>
-      <c r="C40" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="B41" t="s">
-        <v>213</v>
-      </c>
-      <c r="C41" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="B42" t="s">
-        <v>215</v>
-      </c>
-      <c r="C42" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="B43" t="s">
-        <v>217</v>
-      </c>
-      <c r="C43" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="B44" t="s">
-        <v>219</v>
-      </c>
-      <c r="C44" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="B45" t="s">
-        <v>221</v>
-      </c>
-      <c r="C45" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B46" t="s">
-        <v>223</v>
-      </c>
-      <c r="C46" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="B47" t="s">
-        <v>225</v>
-      </c>
-      <c r="C47" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="B48" t="s">
-        <v>227</v>
-      </c>
-      <c r="C48" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="B49" t="s">
-        <v>229</v>
-      </c>
-      <c r="C49" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="B50" t="s">
-        <v>231</v>
-      </c>
-      <c r="C50" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="B51" t="s">
-        <v>233</v>
-      </c>
-      <c r="C51" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B52" t="s">
-        <v>15</v>
-      </c>
-      <c r="C52" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B53" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C54" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
+      <c r="C60" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B61" t="s">
         <v>167</v>
       </c>
-      <c r="C55" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
+      <c r="C61" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B62" t="s">
         <v>169</v>
       </c>
-      <c r="C56" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
+      <c r="C62" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B63" t="s">
         <v>171</v>
       </c>
-      <c r="C57" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
+      <c r="C63" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B64" t="s">
         <v>173</v>
       </c>
-      <c r="C58" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B59" t="s">
-        <v>175</v>
-      </c>
-      <c r="C59" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="B60" t="s">
-        <v>177</v>
-      </c>
-      <c r="C60" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="B61" t="s">
-        <v>179</v>
-      </c>
-      <c r="C61" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="B62" t="s">
-        <v>181</v>
-      </c>
-      <c r="C62" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="B63" t="s">
-        <v>183</v>
-      </c>
-      <c r="C63" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="B64" t="s">
-        <v>185</v>
-      </c>
-      <c r="C64" s="15">
+      <c r="C64" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="s">
-        <v>24</v>
+      <c r="A65" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="B65" t="s">
-        <v>18</v>
-      </c>
-      <c r="C65" s="15">
+        <v>16</v>
+      </c>
+      <c r="C65" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B66" t="s">
+        <v>37</v>
+      </c>
+      <c r="C66" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B67" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B68" t="s">
+        <v>46</v>
+      </c>
+      <c r="C68" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B69" t="s">
+        <v>48</v>
+      </c>
+      <c r="C69" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C66" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
+      <c r="B70" t="s">
+        <v>50</v>
+      </c>
+      <c r="C70" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B71" t="s">
+        <v>52</v>
+      </c>
+      <c r="C71" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B72" t="s">
+        <v>54</v>
+      </c>
+      <c r="C72" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B73" t="s">
         <v>56</v>
       </c>
-      <c r="C67" s="15">
+      <c r="C73" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B74" t="s">
         <v>58</v>
       </c>
-      <c r="C68" s="15">
+      <c r="C74" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B75" t="s">
         <v>60</v>
       </c>
-      <c r="C69" s="15">
+      <c r="C75" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="12" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B76" t="s">
         <v>62</v>
       </c>
-      <c r="C70" s="15">
+      <c r="C76" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B77" t="s">
         <v>64</v>
       </c>
-      <c r="C71" s="15">
+      <c r="C77" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>66</v>
       </c>
-      <c r="C72" s="15">
+      <c r="C78" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>68</v>
       </c>
-      <c r="C73" s="15">
+      <c r="C79" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="12" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>70</v>
       </c>
-      <c r="C74" s="15">
+      <c r="C80" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>72</v>
       </c>
-      <c r="C75" s="15">
+      <c r="C81" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B82" t="s">
         <v>74</v>
       </c>
-      <c r="C76" s="15">
+      <c r="C82" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B83" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="15">
+      <c r="C83" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="12" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B84" t="s">
         <v>78</v>
       </c>
-      <c r="C78" s="15">
+      <c r="C84" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B79" t="s">
-        <v>80</v>
-      </c>
-      <c r="C79" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B80" t="s">
-        <v>82</v>
-      </c>
-      <c r="C80" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B81" t="s">
-        <v>84</v>
-      </c>
-      <c r="C81" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B82" t="s">
-        <v>86</v>
-      </c>
-      <c r="C82" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B83" t="s">
-        <v>88</v>
-      </c>
-      <c r="C83" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B84" t="s">
-        <v>90</v>
-      </c>
-      <c r="C84" s="15">
-        <v>1</v>
-      </c>
-    </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="12" t="s">
-        <v>252</v>
+      <c r="A85" s="9" t="s">
+        <v>240</v>
       </c>
       <c r="B85" t="s">
-        <v>253</v>
-      </c>
-      <c r="C85" s="15">
+        <v>241</v>
+      </c>
+      <c r="C85" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="12" t="s">
-        <v>250</v>
+      <c r="A86" s="9" t="s">
+        <v>238</v>
       </c>
       <c r="B86" t="s">
-        <v>251</v>
-      </c>
-      <c r="C86" s="15">
+        <v>239</v>
+      </c>
+      <c r="C86" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="12" t="s">
-        <v>26</v>
+      <c r="A87" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" s="15">
+        <v>14</v>
+      </c>
+      <c r="C87" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="12" t="s">
-        <v>22</v>
+      <c r="A88" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="B88" t="s">
-        <v>19</v>
-      </c>
-      <c r="C88" s="15">
+        <v>17</v>
+      </c>
+      <c r="C88" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="12" t="s">
-        <v>254</v>
+      <c r="A89" s="9" t="s">
+        <v>242</v>
       </c>
       <c r="B89" t="s">
-        <v>255</v>
-      </c>
-      <c r="C89" s="15">
+        <v>243</v>
+      </c>
+      <c r="C89" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="12" t="s">
+      <c r="A90" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B90" t="s">
+        <v>223</v>
+      </c>
+      <c r="C90" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B91" t="s">
+        <v>225</v>
+      </c>
+      <c r="C91" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B92" t="s">
+        <v>227</v>
+      </c>
+      <c r="C92" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B93" t="s">
+        <v>229</v>
+      </c>
+      <c r="C93" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B94" t="s">
+        <v>231</v>
+      </c>
+      <c r="C94" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B95" t="s">
+        <v>233</v>
+      </c>
+      <c r="C95" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B96" t="s">
         <v>235</v>
       </c>
-      <c r="C90" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="12" t="s">
+      <c r="C96" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B97" t="s">
         <v>237</v>
       </c>
-      <c r="C91" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="B92" t="s">
-        <v>239</v>
-      </c>
-      <c r="C92" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="B93" t="s">
-        <v>241</v>
-      </c>
-      <c r="C93" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="B94" t="s">
-        <v>243</v>
-      </c>
-      <c r="C94" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="B95" t="s">
-        <v>245</v>
-      </c>
-      <c r="C95" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="B96" t="s">
-        <v>247</v>
-      </c>
-      <c r="C96" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="B97" t="s">
-        <v>249</v>
-      </c>
-      <c r="C97" s="15">
+      <c r="C97" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B98" t="s">
-        <v>52</v>
-      </c>
-      <c r="C98" s="15">
+        <v>40</v>
+      </c>
+      <c r="C98" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B99" t="s">
-        <v>51</v>
-      </c>
-      <c r="C99" s="15">
+        <v>39</v>
+      </c>
+      <c r="C99" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>26</v>
+      </c>
+      <c r="B100" t="s">
+        <v>38</v>
+      </c>
+      <c r="C100" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B100" t="s">
-        <v>50</v>
-      </c>
-      <c r="C100" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="12" t="s">
-        <v>30</v>
-      </c>
       <c r="B101" t="s">
-        <v>20</v>
-      </c>
-      <c r="C101" s="15">
+        <v>18</v>
+      </c>
+      <c r="C101" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="12" t="s">
+      <c r="A102" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B102" t="s">
+        <v>89</v>
+      </c>
+      <c r="C102" s="12">
+        <v>2</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B103" t="s">
+        <v>91</v>
+      </c>
+      <c r="C103" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B104" t="s">
+        <v>93</v>
+      </c>
+      <c r="C104" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B105" t="s">
+        <v>95</v>
+      </c>
+      <c r="C105" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B106" t="s">
+        <v>97</v>
+      </c>
+      <c r="C106" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B107" t="s">
+        <v>99</v>
+      </c>
+      <c r="C107" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B108" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="15">
-        <v>2</v>
-      </c>
-      <c r="D102" s="10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="12" t="s">
+      <c r="C108" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B109" t="s">
         <v>103</v>
       </c>
-      <c r="C103" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="12" t="s">
+      <c r="C109" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B110" t="s">
         <v>105</v>
       </c>
-      <c r="C104" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="12" t="s">
+      <c r="C110" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B111" t="s">
         <v>107</v>
       </c>
-      <c r="C105" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="B106" t="s">
-        <v>109</v>
-      </c>
-      <c r="C106" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B107" t="s">
-        <v>111</v>
-      </c>
-      <c r="C107" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B108" t="s">
-        <v>113</v>
-      </c>
-      <c r="C108" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B109" t="s">
-        <v>115</v>
-      </c>
-      <c r="C109" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="B110" t="s">
-        <v>117</v>
-      </c>
-      <c r="C110" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B111" t="s">
-        <v>119</v>
-      </c>
-      <c r="C111" s="15">
+      <c r="C111" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="12" t="s">
-        <v>256</v>
+      <c r="A112" s="9" t="s">
+        <v>244</v>
       </c>
       <c r="B112" t="s">
-        <v>257</v>
-      </c>
-      <c r="C112" s="15" t="s">
-        <v>262</v>
+        <v>245</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="12" t="s">
-        <v>258</v>
+      <c r="A113" s="9" t="s">
+        <v>246</v>
       </c>
       <c r="B113" t="s">
-        <v>259</v>
-      </c>
-      <c r="C113" s="15">
+        <v>247</v>
+      </c>
+      <c r="C113" s="12">
         <v>1</v>
       </c>
     </row>

--- a/static_files/manual.xlsx
+++ b/static_files/manual.xlsx
@@ -6,9 +6,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Uebersicht" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Eventcodes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Abteilungsmapping" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Besprechung" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Uebersicht" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Eventcodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Abteilungsmapping" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -111,6 +112,10 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF1F4E79"/>
       <sz val="10"/>
@@ -131,10 +136,6 @@
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="FF333333"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <sz val="10"/>
     </font>
     <font>
@@ -353,25 +354,25 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -381,15 +382,15 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -487,6 +488,52 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>114300</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>345181</colOff>
+      <row>38</row>
+      <rowOff>19967</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Grafik 1"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="0" y="685800"/>
+          <a:ext cx="16347181" cy="6573167"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -848,6 +895,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
@@ -857,8 +918,8 @@
     <col width="21.42578125" customWidth="1" style="2" min="4" max="4"/>
     <col width="62" customWidth="1" style="2" min="5" max="5"/>
     <col width="39.42578125" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
-    <col width="11.42578125" customWidth="1" style="2" min="7" max="7"/>
-    <col width="11.42578125" customWidth="1" style="2" min="8" max="16384"/>
+    <col width="11.42578125" customWidth="1" style="2" min="7" max="13"/>
+    <col width="11.42578125" customWidth="1" style="2" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1349,7 +1410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1606,7 +1667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/static_files/manual.xlsx
+++ b/static_files/manual.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="600" firstSheet="3" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Besprechung" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="26">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -121,6 +121,17 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Consolas"/>
+      <color rgb="FF1F2937"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="FF1F2937"/>
@@ -143,8 +154,37 @@
       <color rgb="FF1F2937"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="001F2937"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -217,8 +257,62 @@
         <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F4F7"/>
+        <bgColor rgb="00F2F4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5597"/>
+        <bgColor rgb="002F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4C6E7"/>
+        <bgColor rgb="00B4C6E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9EEF4"/>
+        <bgColor rgb="00E9EEF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FAFB"/>
+        <bgColor rgb="00F9FAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00333333"/>
+        <bgColor rgb="00333333"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -300,12 +394,70 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -354,46 +506,85 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -918,8 +1109,8 @@
     <col width="21.42578125" customWidth="1" style="2" min="4" max="4"/>
     <col width="62" customWidth="1" style="2" min="5" max="5"/>
     <col width="39.42578125" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
-    <col width="11.42578125" customWidth="1" style="2" min="7" max="13"/>
-    <col width="11.42578125" customWidth="1" style="2" min="14" max="16384"/>
+    <col width="11.42578125" customWidth="1" style="2" min="7" max="14"/>
+    <col width="11.42578125" customWidth="1" style="2" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/static_files/manual.xlsx
+++ b/static_files/manual.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="600" firstSheet="3" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Besprechung" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="19">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -121,17 +121,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Consolas"/>
-      <color rgb="FF1F2937"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF1F4E79"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="FF1F2937"/>
@@ -154,37 +143,8 @@
       <color rgb="FF1F2937"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00333333"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="001F2937"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="22">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -253,66 +213,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF333333"/>
         <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F4F7"/>
-        <bgColor rgb="00F2F4F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
-        <bgColor rgb="002F5597"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B4C6E7"/>
-        <bgColor rgb="00B4C6E7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E9EEF4"/>
-        <bgColor rgb="00E9EEF4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F9FAFB"/>
-        <bgColor rgb="00F9FAFB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00333333"/>
-        <bgColor rgb="00333333"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -394,70 +306,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -506,19 +360,19 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -527,64 +381,31 @@
     <xf numFmtId="0" fontId="13" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -680,36 +501,91 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
+  <twoCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>114300</rowOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
     </from>
     <to>
       <col>21</col>
       <colOff>345181</colOff>
-      <row>38</row>
-      <rowOff>19967</rowOff>
+      <row>42</row>
+      <rowOff>85998</rowOff>
+    </to>
+    <grpSp>
+      <nvGrpSpPr>
+        <cNvPr id="10" name="Gruppieren 9"/>
+        <cNvGrpSpPr/>
+      </nvGrpSpPr>
+      <grpSpPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="76200"/>
+          <a:ext cx="16347181" cy="8010798"/>
+          <a:chOff x="0" y="47625"/>
+          <a:chExt cx="16347181" cy="8010798"/>
+        </a:xfrm>
+      </grpSpPr>
+      <pic>
+        <nvPicPr>
+          <cNvPr id="8" name="Grafik 7"/>
+          <cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </cNvPicPr>
+        </nvPicPr>
+        <blipFill>
+          <a:blip r:embed="rId1"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </blipFill>
+        <spPr>
+          <a:xfrm>
+            <a:off x="28575" y="6105525"/>
+            <a:ext cx="5992061" cy="1952898"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+      </pic>
+    </grpSp>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>9525</colOff>
+      <row>0</row>
+      <rowOff>47625</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>297548</colOff>
+      <row>31</row>
+      <rowOff>162765</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Grafik 1"/>
+        <cNvPr id="3" name="Grafik 2"/>
         <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="16347181" cy="6573167"/>
+          <a:off x="9525" y="47625"/>
+          <a:ext cx="16290023" cy="6020640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <avLst/>
@@ -1109,8 +985,8 @@
     <col width="21.42578125" customWidth="1" style="2" min="4" max="4"/>
     <col width="62" customWidth="1" style="2" min="5" max="5"/>
     <col width="39.42578125" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
-    <col width="11.42578125" customWidth="1" style="2" min="7" max="14"/>
-    <col width="11.42578125" customWidth="1" style="2" min="15" max="16384"/>
+    <col width="11.42578125" customWidth="1" style="2" min="7" max="25"/>
+    <col width="11.42578125" customWidth="1" style="2" min="26" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1150,7 +1026,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1" s="29">
+    <row r="2" ht="60" customHeight="1" s="31">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Diacos</t>
@@ -1298,7 +1174,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="29">
+    <row r="8" ht="30" customHeight="1" s="31">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Interflex</t>
@@ -1610,12 +1486,12 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="37.28515625" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="29" min="1" max="1"/>
-    <col width="32.7109375" customWidth="1" style="29" min="2" max="2"/>
-    <col width="39.5703125" customWidth="1" style="29" min="3" max="4"/>
+    <col width="18" customWidth="1" style="31" min="1" max="1"/>
+    <col width="32.7109375" customWidth="1" style="31" min="2" max="2"/>
+    <col width="39.5703125" customWidth="1" style="31" min="3" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="29" thickBot="1">
+    <row r="1" ht="15.75" customHeight="1" s="31" thickBot="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Event Code</t>
@@ -1632,7 +1508,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="29" thickBot="1">
+    <row r="2" ht="15.75" customHeight="1" s="31" thickBot="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
           <t>A01</t>
@@ -1649,7 +1525,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.25" customHeight="1" s="29" thickBot="1">
+    <row r="3" ht="29.25" customHeight="1" s="31" thickBot="1">
       <c r="A3" s="17" t="inlineStr">
         <is>
           <t>A02</t>
@@ -1666,7 +1542,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" s="29" thickBot="1">
+    <row r="4" ht="15.75" customHeight="1" s="31" thickBot="1">
       <c r="A4" s="17" t="inlineStr">
         <is>
           <t>A03</t>
@@ -1683,7 +1559,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="29.25" customHeight="1" s="29" thickBot="1">
+    <row r="5" ht="29.25" customHeight="1" s="31" thickBot="1">
       <c r="A5" s="17" t="inlineStr">
         <is>
           <t>A04</t>
@@ -1700,7 +1576,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="29.25" customHeight="1" s="29" thickBot="1">
+    <row r="6" ht="29.25" customHeight="1" s="31" thickBot="1">
       <c r="A6" s="17" t="inlineStr">
         <is>
           <t>A05</t>
@@ -1717,7 +1593,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="29.25" customHeight="1" s="29" thickBot="1">
+    <row r="7" ht="29.25" customHeight="1" s="31" thickBot="1">
       <c r="A7" s="17" t="inlineStr">
         <is>
           <t>A08</t>
@@ -1734,7 +1610,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="29" thickBot="1">
+    <row r="8" ht="15.75" customHeight="1" s="31" thickBot="1">
       <c r="A8" s="17" t="inlineStr">
         <is>
           <t>A11</t>
@@ -1751,7 +1627,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="29" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="31" thickBot="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
           <t>A12</t>
@@ -1768,7 +1644,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="29" thickBot="1">
+    <row r="10" ht="15.75" customHeight="1" s="31" thickBot="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
           <t>A13</t>
@@ -1785,7 +1661,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="33" customHeight="1" s="29" thickBot="1">
+    <row r="11" ht="33" customHeight="1" s="31" thickBot="1">
       <c r="A11" s="17" t="inlineStr">
         <is>
           <t>A14</t>
@@ -1802,7 +1678,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="29" thickBot="1">
+    <row r="12" ht="15.75" customHeight="1" s="31" thickBot="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
           <t>A28</t>
@@ -1819,7 +1695,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="29.25" customHeight="1" s="29" thickBot="1">
+    <row r="13" ht="29.25" customHeight="1" s="31" thickBot="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
           <t>A31</t>
@@ -1836,7 +1712,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="29.25" customHeight="1" s="29" thickBot="1">
+    <row r="14" ht="29.25" customHeight="1" s="31" thickBot="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
           <t>A40</t>
@@ -1867,10 +1743,10 @@
   <dimension ref="A1:Q113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col width="29.28515625" bestFit="1" customWidth="1" style="29" min="1" max="1"/>
-    <col width="16.7109375" bestFit="1" customWidth="1" style="29" min="2" max="2"/>
+    <col width="29.28515625" bestFit="1" customWidth="1" style="31" min="1" max="1"/>
+    <col width="16.7109375" bestFit="1" customWidth="1" style="31" min="2" max="2"/>
     <col width="23.85546875" bestFit="1" customWidth="1" style="12" min="3" max="3"/>
-    <col width="3.42578125" customWidth="1" style="29" min="5" max="5"/>
+    <col width="3.42578125" customWidth="1" style="31" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1889,7 +1765,7 @@
           <t>Stationär(1), Ambulant(2)</t>
         </is>
       </c>
-      <c r="F1" s="28" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>Ab 01.01.2027 wird Opale als ERP eingesetzt. Alle an Orchestra angeschlossende Umsysteme kennen aber die Abteilungsnahmen aus SAP. In der Folge müssen die von Opale gesendeten Abteilungsnahmen (Spalte A) auf den ehemaligen SAP-Abteilungsnahmen (Spalte B) von Orchestra transformiert werden:
 Transformationsregel:

--- a/static_files/manual.xlsx
+++ b/static_files/manual.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -39,12 +39,6 @@
       <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -112,39 +106,58 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FF1F4E79"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <i val="1"/>
       <color rgb="FF1F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <i val="1"/>
       <color rgb="FF333333"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Consolas"/>
+      <family val="3"/>
       <color rgb="FF1F2937"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -160,6 +173,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -224,7 +255,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -244,6 +275,21 @@
       </top>
       <bottom style="medium">
         <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -309,34 +355,31 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -345,67 +388,82 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -505,13 +563,13 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>0</row>
+      <row>1</row>
       <rowOff>76200</rowOff>
     </from>
     <to>
       <col>21</col>
       <colOff>345181</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>85998</rowOff>
     </to>
     <grpSp>
@@ -521,8 +579,8 @@
       </nvGrpSpPr>
       <grpSpPr>
         <a:xfrm rot="0">
-          <a:off x="0" y="76200"/>
-          <a:ext cx="16347181" cy="8010798"/>
+          <a:off x="0" y="266700"/>
+          <a:ext cx="16099531" cy="8010798"/>
           <a:chOff x="0" y="47625"/>
           <a:chExt cx="16347181" cy="8010798"/>
         </a:xfrm>
@@ -559,15 +617,15 @@
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
-      <colOff>9525</colOff>
-      <row>0</row>
+      <colOff>9526</colOff>
+      <row>1</row>
       <rowOff>47625</rowOff>
     </from>
     <to>
-      <col>21</col>
-      <colOff>297548</colOff>
-      <row>31</row>
-      <rowOff>162765</rowOff>
+      <col>20</col>
+      <colOff>771526</colOff>
+      <row>32</row>
+      <rowOff>56314</rowOff>
     </to>
     <pic>
       <nvPicPr>
@@ -584,8 +642,49 @@
       </blipFill>
       <spPr>
         <a:xfrm>
-          <a:off x="9525" y="47625"/>
-          <a:ext cx="16290023" cy="6020640"/>
+          <a:off x="9526" y="238125"/>
+          <a:ext cx="16002000" cy="5914189"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>22</col>
+      <colOff>66675</colOff>
+      <row>1</row>
+      <rowOff>47625</rowOff>
+    </from>
+    <to>
+      <col>33</col>
+      <colOff>67845</colOff>
+      <row>22</row>
+      <rowOff>67236</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Grafik 3"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="16411575" y="238125"/>
+          <a:ext cx="8383170" cy="4020111"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <avLst/>
@@ -606,7 +705,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>18</row>
       <rowOff>104775</rowOff>
     </from>
     <ext cx="8954750" cy="4686954"/>
@@ -962,10 +1061,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AJ39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="12.140625" customWidth="1" style="35" min="21" max="21"/>
+    <col width="0.7109375" customWidth="1" style="20" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>Opale</t>
+        </is>
+      </c>
+      <c r="W1" s="36" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="n"/>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
+      <c r="I2" s="19" t="n"/>
+      <c r="J2" s="19" t="n"/>
+      <c r="K2" s="19" t="n"/>
+      <c r="L2" s="19" t="n"/>
+      <c r="M2" s="19" t="n"/>
+      <c r="N2" s="19" t="n"/>
+      <c r="O2" s="19" t="n"/>
+      <c r="P2" s="19" t="n"/>
+      <c r="Q2" s="19" t="n"/>
+      <c r="R2" s="19" t="n"/>
+      <c r="S2" s="19" t="n"/>
+      <c r="T2" s="19" t="n"/>
+      <c r="U2" s="19" t="n"/>
+    </row>
+    <row r="24">
+      <c r="W24" s="21" t="inlineStr">
+        <is>
+          <t>-Polypoint verwendet dat-File, Interflex verwendet txt-File, Ines verwendet HL7/Expopa10, alle anderen Systeme HL7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="W25" s="21" t="inlineStr">
+        <is>
+          <t>-Die Fach. OE wird heute an die Umsysteme geliefert und entspricht der Abteilung INES in Opale</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="W26" s="21" t="inlineStr">
+        <is>
+          <t>-Die Umsysteme (HL7) empfangen die Fach.OE heute im Feld PV1_3.4 Facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="W27" s="21" t="inlineStr">
+        <is>
+          <t>-SAP sendet heute die Fach. OE im Format F_XXXX (z.B F_OHR1A) an die Umsysteme</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="J34" s="21" t="inlineStr">
+        <is>
+          <t>-Opale sendet das Feld Abteilung im HL7-File im Feld PV1_3.5 Location Status</t>
+        </is>
+      </c>
+      <c r="AI34" s="22" t="n"/>
+      <c r="AJ34" s="22" t="n"/>
+    </row>
+    <row r="35">
+      <c r="J35" s="21" t="inlineStr">
+        <is>
+          <t>-Abteilung INES in Opale entspricht dem Feld Fach. OE in SAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="J36" s="21" t="inlineStr">
+        <is>
+          <t>-Opale sendet das benutzerspezifische Feld Abteilung INES im HL7-File im Feld PV2_41.3 (spitalspezifisches Feld)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="J37" s="21" t="inlineStr">
+        <is>
+          <t>-Opale sendet Abteilung Ines im Format XXXX (z.B OHR1A) an die Umsysteme</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="P39" s="23" t="n"/>
+      <c r="Q39" s="23" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="W1:AG1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -976,17 +1182,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col width="14.7109375" customWidth="1" style="2" min="1" max="1"/>
     <col width="6.7109375" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
     <col width="19.42578125" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="21.42578125" customWidth="1" style="2" min="4" max="4"/>
-    <col width="62" customWidth="1" style="2" min="5" max="5"/>
+    <col width="17.7109375" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="60.7109375" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
     <col width="39.42578125" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
-    <col width="11.42578125" customWidth="1" style="2" min="7" max="25"/>
-    <col width="11.42578125" customWidth="1" style="2" min="26" max="16384"/>
+    <col width="18.5703125" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
+    <col width="11.42578125" customWidth="1" style="2" min="8" max="31"/>
+    <col width="11.42578125" customWidth="1" style="2" min="32" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1017,16 +1224,21 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Anassung wegen neuen SAP OE notwendig</t>
+          <t>Verwendet Abteilung INES von Opale</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>Fileformat</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>Todos</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1" s="31">
+    <row r="2" ht="60" customHeight="1" s="35">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Diacos</t>
@@ -1050,6 +1262,11 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Nein</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>HL7</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1299,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>dat</t>
         </is>
       </c>
     </row>
@@ -1108,6 +1325,11 @@
           <t>Nein</t>
         </is>
       </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>HL7</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1129,6 +1351,11 @@
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Ja</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>HL7 (neu Expopa10)</t>
         </is>
       </c>
     </row>
@@ -1150,6 +1377,11 @@
           <t>Ja</t>
         </is>
       </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>HL7</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1173,8 +1405,13 @@
           <t>Ja</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" s="31">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>HL7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="35">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Interflex</t>
@@ -1205,7 +1442,12 @@
           <t>Nein</t>
         </is>
       </c>
-      <c r="G8" s="13" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1227,6 +1469,11 @@
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Nein</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>HL7</t>
         </is>
       </c>
     </row>
@@ -1248,6 +1495,11 @@
           <t>Nein</t>
         </is>
       </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>HL7</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1269,6 +1521,11 @@
       <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Nein</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>HL7</t>
         </is>
       </c>
     </row>
@@ -1290,6 +1547,11 @@
           <t>Nein</t>
         </is>
       </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>HL7</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1309,157 +1571,151 @@
           <t>Nein</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>ID-Diacos-Absprung</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="1" t="n"/>
-      <c r="E14" s="3" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>HL7</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="E15" s="6" t="n"/>
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Interflex</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="15" t="n"/>
+      <c r="K15" s="15" t="n"/>
+      <c r="L15" s="15" t="n"/>
+      <c r="M15" s="15" t="n"/>
+      <c r="N15" s="15" t="n"/>
+      <c r="O15" s="15" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>URL Prod</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>IF 6040</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Interflex</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="16" t="n"/>
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="16" t="n"/>
-      <c r="J17" s="16" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="16" t="n"/>
-      <c r="M17" s="16" t="n"/>
-      <c r="N17" s="16" t="n"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bei stationären wie auch ambulanten Patienten wird in der Regel immer der Besucher (Stammdaten des Patienten), sowie auch der Besuch (mit Gültigkeitsdauer, Zimmer, Bett, Zutrittsrechten etc.) angelegt</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Allerdings gibt es in Interflex eine Logik, dass bei ambulanten Fällen der Besuch nur angelegt wird, wenn die Abteilung in Interflex unter ambulante Fälle erfasst ist</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>CDMS</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="n"/>
+      <c r="C46" s="15" t="n"/>
+      <c r="D46" s="15" t="n"/>
+      <c r="E46" s="15" t="n"/>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="15" t="n"/>
+      <c r="H46" s="15" t="n"/>
+      <c r="I46" s="15" t="n"/>
+      <c r="J46" s="15" t="n"/>
+      <c r="K46" s="15" t="n"/>
+      <c r="L46" s="15" t="n"/>
+      <c r="M46" s="15" t="n"/>
+      <c r="N46" s="15" t="n"/>
+      <c r="O46" s="15" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>URL Prod</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>IF 6040</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Bei stationären wie auch ambulanten Patienten wird in der Regel immer der Besucher (Stammdaten des Patienten), sowie auch der Besuch (mit Gültigkeitsdauer, Zimmer, Bett, Zutrittsrechten etc.) angelegt</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Allerdings gibt es in Interflex eine Logik, dass bei ambulanten Fällen der Besuch nur angelegt wird, wenn die Abteilung in Interflex unter ambulante Fälle erfasst ist</t>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>RKB i-engine</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>CDMS</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
-      <c r="G48" s="16" t="n"/>
-      <c r="H48" s="16" t="n"/>
-      <c r="I48" s="16" t="n"/>
-      <c r="J48" s="16" t="n"/>
-      <c r="K48" s="16" t="n"/>
-      <c r="L48" s="16" t="n"/>
-      <c r="M48" s="16" t="n"/>
-      <c r="N48" s="16" t="n"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>URL Test</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>von CDMS Server starten</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>URL Prod</t>
-        </is>
-      </c>
-      <c r="B49" s="14" t="inlineStr">
-        <is>
-          <t>RKB i-engine</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+          <t>Ablage Testsystem</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>\\rehabellikon.ch\dfs\CDMS_TEST_TRANSFER</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>IBIcare</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="n"/>
+      <c r="C52" s="15" t="n"/>
+      <c r="D52" s="15" t="n"/>
+      <c r="E52" s="15" t="n"/>
+      <c r="F52" s="15" t="n"/>
+      <c r="G52" s="15" t="n"/>
+      <c r="H52" s="15" t="n"/>
+      <c r="I52" s="15" t="n"/>
+      <c r="J52" s="15" t="n"/>
+      <c r="K52" s="15" t="n"/>
+      <c r="L52" s="15" t="n"/>
+      <c r="M52" s="15" t="n"/>
+      <c r="N52" s="15" t="n"/>
+      <c r="O52" s="15" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>URL Test</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>von CDMS Server starten</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Ablage Testsystem</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>\\rehabellikon.ch\dfs\CDMS_TEST_TRANSFER</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>IBIcare</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="16" t="n"/>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
-      <c r="G54" s="16" t="n"/>
-      <c r="H54" s="16" t="n"/>
-      <c r="I54" s="16" t="n"/>
-      <c r="J54" s="16" t="n"/>
-      <c r="K54" s="16" t="n"/>
-      <c r="L54" s="16" t="n"/>
-      <c r="M54" s="16" t="n"/>
-      <c r="N54" s="16" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>URL Test</t>
-        </is>
-      </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>IBI-care - Reha Bellikon TEST</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B14">
+  <conditionalFormatting sqref="A2:B13">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$D2="x"</formula>
     </cfRule>
@@ -1468,9 +1724,9 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" display="https://interflex.rehabellikon.ch/IF6040/IFWebLogin.aspx?ReturnUrl=%2fIF6040%2fWelcome.aspx" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" display="https://cdmsprod.rehabellikon.ch/auth-service/authenticate/start?spnego=failed&amp;application=tsclient&amp;path=%23/main" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" display="https://ibi-care-test.rehabellikon.ch/IBI-care/login?notAuthenticated=true&amp;returnUrl=%2F" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" display="https://interflex.rehabellikon.ch/IF6040/IFWebLogin.aspx?ReturnUrl=%2fIF6040%2fWelcome.aspx" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" display="https://cdmsprod.rehabellikon.ch/auth-service/authenticate/start?spnego=failed&amp;application=tsclient&amp;path=%23/main" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" display="https://ibi-care-test.rehabellikon.ch/IBI-care/login?notAuthenticated=true&amp;returnUrl=%2F" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
@@ -1486,244 +1742,244 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="37.28515625" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="31" min="1" max="1"/>
-    <col width="32.7109375" customWidth="1" style="31" min="2" max="2"/>
-    <col width="39.5703125" customWidth="1" style="31" min="3" max="4"/>
+    <col width="18" customWidth="1" style="35" min="1" max="1"/>
+    <col width="32.7109375" customWidth="1" style="35" min="2" max="2"/>
+    <col width="39.5703125" customWidth="1" style="35" min="3" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="31" thickBot="1">
-      <c r="A1" s="19" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="35" thickBot="1">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>Event Code</t>
         </is>
       </c>
-      <c r="B1" s="19" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>Bedeutung</t>
         </is>
       </c>
-      <c r="C1" s="19" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>Typischer Usecase</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="31" thickBot="1">
-      <c r="A2" s="17" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="35" thickBot="1">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>A01</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Admission / Visit Notification</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>Stationäre Aufnahme eines Patienten</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="29.25" customHeight="1" s="31" thickBot="1">
-      <c r="A3" s="17" t="inlineStr">
+    <row r="3" ht="29.25" customHeight="1" s="35" thickBot="1">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>A02</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Transfer a Patient</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Verlegung (z. B. Betten-/Stationenwechsel)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" s="31" thickBot="1">
-      <c r="A4" s="17" t="inlineStr">
+    <row r="4" ht="15.75" customHeight="1" s="35" thickBot="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Discharge / End Visit</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Entlassung des Patienten</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="29.25" customHeight="1" s="31" thickBot="1">
-      <c r="A5" s="17" t="inlineStr">
+    <row r="5" ht="29.25" customHeight="1" s="35" thickBot="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>A04</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Register a Patient</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Ambulante Registrierung / Notfall-Aufnahme</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="29.25" customHeight="1" s="31" thickBot="1">
-      <c r="A6" s="17" t="inlineStr">
+    <row r="6" ht="29.25" customHeight="1" s="35" thickBot="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>A05</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Pre-Admit a Patient</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Voraufnahme / Präregistrierung eines Patienten</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="29.25" customHeight="1" s="31" thickBot="1">
-      <c r="A7" s="17" t="inlineStr">
+    <row r="7" ht="29.25" customHeight="1" s="35" thickBot="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>A08</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Update Patient Information</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Änderung von Stammdaten oder Falldaten</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="31" thickBot="1">
-      <c r="A8" s="17" t="inlineStr">
+    <row r="8" ht="15.75" customHeight="1" s="35" thickBot="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>A11</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Cancel Admission</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Stornierung einer Aufnahme (A01/A04)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="31" thickBot="1">
-      <c r="A9" s="17" t="inlineStr">
+    <row r="9" ht="15.75" customHeight="1" s="35" thickBot="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>A12</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Cancel Transfer</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Stornierung einer Verlegung</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="31" thickBot="1">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="35" thickBot="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>A13</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Cancel Discharge</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>Stornierung einer Entlassung</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="33" customHeight="1" s="31" thickBot="1">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="11" ht="33" customHeight="1" s="35" thickBot="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>A14</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Pending Admit</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Geplante / Ausstehende Aufnahme)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="31" thickBot="1">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="12" ht="15.75" customHeight="1" s="35" thickBot="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>A28</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Add Person Information</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Personenstammdaten anlegen</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="29.25" customHeight="1" s="31" thickBot="1">
-      <c r="A13" s="17" t="inlineStr">
+    <row r="13" ht="29.25" customHeight="1" s="35" thickBot="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>A31</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Update Person Information</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Reine Personen-Stammdatenänderung (ohne Fallbezug)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="29.25" customHeight="1" s="31" thickBot="1">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="14" ht="29.25" customHeight="1" s="35" thickBot="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>A40</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Merge Patient - Patient ID</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Zusammenführung von zwei Patientenakten (Dublettenbereinigung)</t>
         </is>
@@ -1743,29 +1999,29 @@
   <dimension ref="A1:Q113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col width="29.28515625" bestFit="1" customWidth="1" style="31" min="1" max="1"/>
-    <col width="16.7109375" bestFit="1" customWidth="1" style="31" min="2" max="2"/>
-    <col width="23.85546875" bestFit="1" customWidth="1" style="12" min="3" max="3"/>
-    <col width="3.42578125" customWidth="1" style="31" min="5" max="5"/>
+    <col width="29.28515625" bestFit="1" customWidth="1" style="35" min="1" max="1"/>
+    <col width="16.7109375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
+    <col width="23.85546875" bestFit="1" customWidth="1" style="11" min="3" max="3"/>
+    <col width="3.42578125" customWidth="1" style="35" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Orchestra Input (Opale Output)</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Orchestra Output</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Stationär(1), Ambulant(2)</t>
         </is>
       </c>
-      <c r="F1" s="30" t="inlineStr">
+      <c r="F1" s="37" t="inlineStr">
         <is>
           <t>Ab 01.01.2027 wird Opale als ERP eingesetzt. Alle an Orchestra angeschlossende Umsysteme kennen aber die Abteilungsnahmen aus SAP. In der Folge müssen die von Opale gesendeten Abteilungsnahmen (Spalte A) auf den ehemaligen SAP-Abteilungsnahmen (Spalte B) von Orchestra transformiert werden:
 Transformationsregel:
@@ -1775,7 +2031,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>AR1A</t>
         </is>
@@ -1785,12 +2041,12 @@
           <t>F_AR1A</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n">
+      <c r="C2" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>AR1B</t>
         </is>
@@ -1800,12 +2056,12 @@
           <t>F_AR1B</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n">
+      <c r="C3" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>AR2A</t>
         </is>
@@ -1815,12 +2071,12 @@
           <t>F_AR2A</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>ARBE</t>
         </is>
@@ -1830,14 +2086,14 @@
           <t>F_ARBE</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>BB01</t>
         </is>
@@ -1847,12 +2103,12 @@
           <t>F_BB01</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>BB02</t>
         </is>
@@ -1862,12 +2118,12 @@
           <t>F_BB02</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>BB03</t>
         </is>
@@ -1877,12 +2133,12 @@
           <t>F_BB03</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>BB04</t>
         </is>
@@ -1892,12 +2148,12 @@
           <t>F_BB04</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>BB05</t>
         </is>
@@ -1907,12 +2163,12 @@
           <t>F_BB05</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>BB06</t>
         </is>
@@ -1922,12 +2178,12 @@
           <t>F_BB06</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">BB07  </t>
         </is>
@@ -1937,12 +2193,12 @@
           <t xml:space="preserve">F_BB07  </t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">BB08  </t>
         </is>
@@ -1952,12 +2208,12 @@
           <t xml:space="preserve">F_BB08  </t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>BM01</t>
         </is>
@@ -1967,12 +2223,12 @@
           <t>F_BM01</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>BM02</t>
         </is>
@@ -1982,12 +2238,12 @@
           <t>F_BM02</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>BM03</t>
         </is>
@@ -1997,12 +2253,12 @@
           <t>F_BM03</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>BM04</t>
         </is>
@@ -2012,12 +2268,12 @@
           <t>F_BM04</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>BM05</t>
         </is>
@@ -2027,12 +2283,12 @@
           <t>F_BM05</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>BM06</t>
         </is>
@@ -2042,12 +2298,12 @@
           <t>F_BM06</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>BM07</t>
         </is>
@@ -2057,12 +2313,12 @@
           <t>F_BM07</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>BM08</t>
         </is>
@@ -2072,12 +2328,12 @@
           <t>F_BM08</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>BM09</t>
         </is>
@@ -2087,12 +2343,12 @@
           <t>F_BM09</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>BM10</t>
         </is>
@@ -2102,12 +2358,12 @@
           <t>F_BM10</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>BM11</t>
         </is>
@@ -2117,12 +2373,12 @@
           <t>F_BM11</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>BM12</t>
         </is>
@@ -2132,12 +2388,12 @@
           <t>F_BM12</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C25" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">BM13  </t>
         </is>
@@ -2147,12 +2403,12 @@
           <t xml:space="preserve">F_BM13  </t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">BM14  </t>
         </is>
@@ -2162,12 +2418,12 @@
           <t xml:space="preserve">F_BM14  </t>
         </is>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>BOT01</t>
         </is>
@@ -2177,12 +2433,12 @@
           <t>F_BOT01</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>BOT02</t>
         </is>
@@ -2192,12 +2448,12 @@
           <t>F_BOT02</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>BOT03</t>
         </is>
@@ -2207,12 +2463,12 @@
           <t>F_BOT03</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>BOT04</t>
         </is>
@@ -2222,12 +2478,12 @@
           <t>F_BOT04</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n">
+      <c r="C31" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>BOT05</t>
         </is>
@@ -2237,12 +2493,12 @@
           <t>F_BOT05</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n">
+      <c r="C32" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>BOT06</t>
         </is>
@@ -2252,12 +2508,12 @@
           <t>F_BOT06</t>
         </is>
       </c>
-      <c r="C33" s="12" t="n">
+      <c r="C33" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>BOT07</t>
         </is>
@@ -2267,12 +2523,12 @@
           <t>F_BOT07</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n">
+      <c r="C34" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>BOT08</t>
         </is>
@@ -2282,12 +2538,12 @@
           <t>F_BOT08</t>
         </is>
       </c>
-      <c r="C35" s="12" t="n">
+      <c r="C35" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>BOT09</t>
         </is>
@@ -2297,12 +2553,12 @@
           <t>F_BOT09</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="C36" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>BOT10</t>
         </is>
@@ -2312,12 +2568,12 @@
           <t>F_BOT10</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n">
+      <c r="C37" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">BOT11 </t>
         </is>
@@ -2327,12 +2583,12 @@
           <t xml:space="preserve">F_BOT11 </t>
         </is>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C38" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">BOT12 </t>
         </is>
@@ -2342,12 +2598,12 @@
           <t xml:space="preserve">F_BOT12 </t>
         </is>
       </c>
-      <c r="C39" s="12" t="n">
+      <c r="C39" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>CH01</t>
         </is>
@@ -2357,12 +2613,12 @@
           <t>F_CH01</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n">
+      <c r="C40" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>CH02</t>
         </is>
@@ -2372,12 +2628,12 @@
           <t>F_CH02</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n">
+      <c r="C41" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>CH03</t>
         </is>
@@ -2387,12 +2643,12 @@
           <t>F_CH03</t>
         </is>
       </c>
-      <c r="C42" s="12" t="n">
+      <c r="C42" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>CH04</t>
         </is>
@@ -2402,12 +2658,12 @@
           <t>F_CH04</t>
         </is>
       </c>
-      <c r="C43" s="12" t="n">
+      <c r="C43" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>CH05</t>
         </is>
@@ -2417,12 +2673,12 @@
           <t>F_CH05</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n">
+      <c r="C44" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>CH06</t>
         </is>
@@ -2432,12 +2688,12 @@
           <t>F_CH06</t>
         </is>
       </c>
-      <c r="C45" s="12" t="n">
+      <c r="C45" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>CH07</t>
         </is>
@@ -2447,12 +2703,12 @@
           <t>F_CH07</t>
         </is>
       </c>
-      <c r="C46" s="12" t="n">
+      <c r="C46" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>CH08</t>
         </is>
@@ -2462,12 +2718,12 @@
           <t>F_CH08</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n">
+      <c r="C47" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>CH09</t>
         </is>
@@ -2477,12 +2733,12 @@
           <t>F_CH09</t>
         </is>
       </c>
-      <c r="C48" s="12" t="n">
+      <c r="C48" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>CH10</t>
         </is>
@@ -2492,12 +2748,12 @@
           <t>F_CH10</t>
         </is>
       </c>
-      <c r="C49" s="12" t="n">
+      <c r="C49" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>CH11</t>
         </is>
@@ -2507,12 +2763,12 @@
           <t>F_CH11</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n">
+      <c r="C50" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>CH12</t>
         </is>
@@ -2522,12 +2778,12 @@
           <t>F_CH12</t>
         </is>
       </c>
-      <c r="C51" s="12" t="n">
+      <c r="C51" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>EFLGUT</t>
         </is>
@@ -2537,12 +2793,12 @@
           <t>F_EFLGUT</t>
         </is>
       </c>
-      <c r="C52" s="12" t="n">
+      <c r="C52" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>ERGO</t>
         </is>
@@ -2552,27 +2808,27 @@
           <t>F_ERGO</t>
         </is>
       </c>
-      <c r="C53" s="12" t="n">
+      <c r="C53" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>F_NRUR</t>
         </is>
       </c>
-      <c r="C54" s="12" t="n">
+      <c r="C54" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>JC01</t>
         </is>
@@ -2582,12 +2838,12 @@
           <t>F_JC01</t>
         </is>
       </c>
-      <c r="C55" s="12" t="n">
+      <c r="C55" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>JC02</t>
         </is>
@@ -2597,12 +2853,12 @@
           <t>F_JC02</t>
         </is>
       </c>
-      <c r="C56" s="12" t="n">
+      <c r="C56" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>JC03</t>
         </is>
@@ -2612,12 +2868,12 @@
           <t>F_JC03</t>
         </is>
       </c>
-      <c r="C57" s="12" t="n">
+      <c r="C57" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>JC04</t>
         </is>
@@ -2627,12 +2883,12 @@
           <t>F_JC04</t>
         </is>
       </c>
-      <c r="C58" s="12" t="n">
+      <c r="C58" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>JC05</t>
         </is>
@@ -2642,12 +2898,12 @@
           <t>F_JC05</t>
         </is>
       </c>
-      <c r="C59" s="12" t="n">
+      <c r="C59" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>JC06</t>
         </is>
@@ -2657,12 +2913,12 @@
           <t>F_JC06</t>
         </is>
       </c>
-      <c r="C60" s="12" t="n">
+      <c r="C60" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>JC07</t>
         </is>
@@ -2672,12 +2928,12 @@
           <t>F_JC07</t>
         </is>
       </c>
-      <c r="C61" s="12" t="n">
+      <c r="C61" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>JC08</t>
         </is>
@@ -2687,12 +2943,12 @@
           <t>F_JC08</t>
         </is>
       </c>
-      <c r="C62" s="12" t="n">
+      <c r="C62" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">JC09  </t>
         </is>
@@ -2702,12 +2958,12 @@
           <t xml:space="preserve">F_JC09  </t>
         </is>
       </c>
-      <c r="C63" s="12" t="n">
+      <c r="C63" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">JC10  </t>
         </is>
@@ -2717,12 +2973,12 @@
           <t xml:space="preserve">F_JC10  </t>
         </is>
       </c>
-      <c r="C64" s="12" t="n">
+      <c r="C64" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>LOGO</t>
         </is>
@@ -2732,7 +2988,7 @@
           <t>F_LOGO</t>
         </is>
       </c>
-      <c r="C65" s="12" t="n">
+      <c r="C65" s="11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2747,12 +3003,12 @@
           <t>F_NEUROP</t>
         </is>
       </c>
-      <c r="C66" s="12" t="n">
+      <c r="C66" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>NR1</t>
         </is>
@@ -2762,12 +3018,12 @@
           <t>F_NR1</t>
         </is>
       </c>
-      <c r="C67" s="12" t="n">
+      <c r="C67" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>NR2</t>
         </is>
@@ -2777,12 +3033,12 @@
           <t>F_NR2</t>
         </is>
       </c>
-      <c r="C68" s="12" t="n">
+      <c r="C68" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>NR3</t>
         </is>
@@ -2792,12 +3048,12 @@
           <t>F_NR3</t>
         </is>
       </c>
-      <c r="C69" s="12" t="n">
+      <c r="C69" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="inlineStr">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>NR4</t>
         </is>
@@ -2807,12 +3063,12 @@
           <t>F_NR4</t>
         </is>
       </c>
-      <c r="C70" s="12" t="n">
+      <c r="C70" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="A71" s="8" t="inlineStr">
         <is>
           <t>NR5</t>
         </is>
@@ -2822,12 +3078,12 @@
           <t>F_NR5</t>
         </is>
       </c>
-      <c r="C71" s="12" t="n">
+      <c r="C71" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>NR6</t>
         </is>
@@ -2837,12 +3093,12 @@
           <t>F_NR6</t>
         </is>
       </c>
-      <c r="C72" s="12" t="n">
+      <c r="C72" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>NR7</t>
         </is>
@@ -2852,12 +3108,12 @@
           <t>F_NR7</t>
         </is>
       </c>
-      <c r="C73" s="12" t="n">
+      <c r="C73" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>NR8</t>
         </is>
@@ -2867,12 +3123,12 @@
           <t>F_NR8</t>
         </is>
       </c>
-      <c r="C74" s="12" t="n">
+      <c r="C74" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>OHR1A</t>
         </is>
@@ -2882,12 +3138,12 @@
           <t>F_OHR1A</t>
         </is>
       </c>
-      <c r="C75" s="12" t="n">
+      <c r="C75" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>OHR1B</t>
         </is>
@@ -2897,12 +3153,12 @@
           <t>F_OHR1B</t>
         </is>
       </c>
-      <c r="C76" s="12" t="n">
+      <c r="C76" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="inlineStr">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>OHR2A</t>
         </is>
@@ -2912,12 +3168,12 @@
           <t>F_OHR2A</t>
         </is>
       </c>
-      <c r="C77" s="12" t="n">
+      <c r="C77" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="A78" s="8" t="inlineStr">
         <is>
           <t>OHR2B</t>
         </is>
@@ -2927,12 +3183,12 @@
           <t>F_OHR2B</t>
         </is>
       </c>
-      <c r="C78" s="12" t="n">
+      <c r="C78" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>OHR3A</t>
         </is>
@@ -2942,12 +3198,12 @@
           <t>F_OHR3A</t>
         </is>
       </c>
-      <c r="C79" s="12" t="n">
+      <c r="C79" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>OHR3B</t>
         </is>
@@ -2957,12 +3213,12 @@
           <t>F_OHR3B</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C80" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="inlineStr">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t>OHR4A</t>
         </is>
@@ -2972,12 +3228,12 @@
           <t>F_OHR4A</t>
         </is>
       </c>
-      <c r="C81" s="12" t="n">
+      <c r="C81" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>OHR4B</t>
         </is>
@@ -2987,12 +3243,12 @@
           <t>F_OHR4B</t>
         </is>
       </c>
-      <c r="C82" s="12" t="n">
+      <c r="C82" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t>OHR5A</t>
         </is>
@@ -3002,12 +3258,12 @@
           <t>F_OHR5A</t>
         </is>
       </c>
-      <c r="C83" s="12" t="n">
+      <c r="C83" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="inlineStr">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>OHR5B</t>
         </is>
@@ -3017,12 +3273,12 @@
           <t>F_OHR5B</t>
         </is>
       </c>
-      <c r="C84" s="12" t="n">
+      <c r="C84" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="inlineStr">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>OHROS</t>
         </is>
@@ -3032,12 +3288,12 @@
           <t>F_OHROS</t>
         </is>
       </c>
-      <c r="C85" s="12" t="n">
+      <c r="C85" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="inlineStr">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t>OHROT</t>
         </is>
@@ -3047,12 +3303,12 @@
           <t>F_OHROT</t>
         </is>
       </c>
-      <c r="C86" s="12" t="n">
+      <c r="C86" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="inlineStr">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t>PHYSIO</t>
         </is>
@@ -3062,12 +3318,12 @@
           <t>F_PHYSIO</t>
         </is>
       </c>
-      <c r="C87" s="12" t="n">
+      <c r="C87" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>PSYCH</t>
         </is>
@@ -3077,12 +3333,12 @@
           <t>F_PSYCH</t>
         </is>
       </c>
-      <c r="C88" s="12" t="n">
+      <c r="C88" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="inlineStr">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>RADIOL</t>
         </is>
@@ -3092,12 +3348,12 @@
           <t>F_RADIOL</t>
         </is>
       </c>
-      <c r="C89" s="12" t="n">
+      <c r="C89" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="inlineStr">
+      <c r="A90" s="8" t="inlineStr">
         <is>
           <t>SG01</t>
         </is>
@@ -3107,12 +3363,12 @@
           <t>F_SG01</t>
         </is>
       </c>
-      <c r="C90" s="12" t="n">
+      <c r="C90" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="inlineStr">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>SG02</t>
         </is>
@@ -3122,12 +3378,12 @@
           <t>F_SG02</t>
         </is>
       </c>
-      <c r="C91" s="12" t="n">
+      <c r="C91" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="inlineStr">
+      <c r="A92" s="8" t="inlineStr">
         <is>
           <t>SG03</t>
         </is>
@@ -3137,12 +3393,12 @@
           <t>F_SG03</t>
         </is>
       </c>
-      <c r="C92" s="12" t="n">
+      <c r="C92" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
+      <c r="A93" s="8" t="inlineStr">
         <is>
           <t>SG04</t>
         </is>
@@ -3152,12 +3408,12 @@
           <t>F_SG04</t>
         </is>
       </c>
-      <c r="C93" s="12" t="n">
+      <c r="C93" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="inlineStr">
+      <c r="A94" s="8" t="inlineStr">
         <is>
           <t>SG05</t>
         </is>
@@ -3167,12 +3423,12 @@
           <t>F_SG05</t>
         </is>
       </c>
-      <c r="C94" s="12" t="n">
+      <c r="C94" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="inlineStr">
+      <c r="A95" s="8" t="inlineStr">
         <is>
           <t>SG06</t>
         </is>
@@ -3182,12 +3438,12 @@
           <t>F_SG06</t>
         </is>
       </c>
-      <c r="C95" s="12" t="n">
+      <c r="C95" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="inlineStr">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>SG08</t>
         </is>
@@ -3197,12 +3453,12 @@
           <t>F_SG08</t>
         </is>
       </c>
-      <c r="C96" s="12" t="n">
+      <c r="C96" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="inlineStr">
+      <c r="A97" s="8" t="inlineStr">
         <is>
           <t>SG09</t>
         </is>
@@ -3212,7 +3468,7 @@
           <t>F_SG09</t>
         </is>
       </c>
-      <c r="C97" s="12" t="n">
+      <c r="C97" s="11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3227,7 +3483,7 @@
           <t>F_SMRLPM</t>
         </is>
       </c>
-      <c r="C98" s="12" t="n">
+      <c r="C98" s="11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3242,7 +3498,7 @@
           <t>F_SMRPHY</t>
         </is>
       </c>
-      <c r="C99" s="12" t="n">
+      <c r="C99" s="11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3257,12 +3513,12 @@
           <t>F_SMRTAR</t>
         </is>
       </c>
-      <c r="C100" s="12" t="n">
+      <c r="C100" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="inlineStr">
+      <c r="A101" s="8" t="inlineStr">
         <is>
           <t>TARDOC</t>
         </is>
@@ -3272,12 +3528,12 @@
           <t>F_TARDOC</t>
         </is>
       </c>
-      <c r="C101" s="12" t="n">
+      <c r="C101" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="9" t="inlineStr">
+      <c r="A102" s="8" t="inlineStr">
         <is>
           <t>TR1AMK</t>
         </is>
@@ -3287,17 +3543,17 @@
           <t>F_TR1AMK</t>
         </is>
       </c>
-      <c r="C102" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="C102" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
         <is>
           <t>(Ausname!)</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="inlineStr">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t>TR1BMK</t>
         </is>
@@ -3307,12 +3563,12 @@
           <t>F_TR1BMK</t>
         </is>
       </c>
-      <c r="C103" s="12" t="n">
+      <c r="C103" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="inlineStr">
+      <c r="A104" s="8" t="inlineStr">
         <is>
           <t>TR2AMK</t>
         </is>
@@ -3322,12 +3578,12 @@
           <t>F_TR2AMK</t>
         </is>
       </c>
-      <c r="C104" s="12" t="n">
+      <c r="C104" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="inlineStr">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t>TR2BMK</t>
         </is>
@@ -3337,12 +3593,12 @@
           <t>F_TR2BMK</t>
         </is>
       </c>
-      <c r="C105" s="12" t="n">
+      <c r="C105" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="inlineStr">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>TR3AMK</t>
         </is>
@@ -3352,12 +3608,12 @@
           <t>F_TR3AMK</t>
         </is>
       </c>
-      <c r="C106" s="12" t="n">
+      <c r="C106" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="inlineStr">
+      <c r="A107" s="8" t="inlineStr">
         <is>
           <t>TR3BMK</t>
         </is>
@@ -3367,12 +3623,12 @@
           <t>F_TR3BMK</t>
         </is>
       </c>
-      <c r="C107" s="12" t="n">
+      <c r="C107" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="inlineStr">
+      <c r="A108" s="8" t="inlineStr">
         <is>
           <t>TR4AMK</t>
         </is>
@@ -3382,12 +3638,12 @@
           <t>F_TR4AMK</t>
         </is>
       </c>
-      <c r="C108" s="12" t="n">
+      <c r="C108" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="inlineStr">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t>TR4BMK</t>
         </is>
@@ -3397,12 +3653,12 @@
           <t>F_TR4BMK</t>
         </is>
       </c>
-      <c r="C109" s="12" t="n">
+      <c r="C109" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="inlineStr">
+      <c r="A110" s="8" t="inlineStr">
         <is>
           <t>TR5AMK</t>
         </is>
@@ -3412,12 +3668,12 @@
           <t>F_TR5AMK</t>
         </is>
       </c>
-      <c r="C110" s="12" t="n">
+      <c r="C110" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="inlineStr">
+      <c r="A111" s="8" t="inlineStr">
         <is>
           <t>TR5BMK</t>
         </is>
@@ -3427,12 +3683,12 @@
           <t>F_TR5BMK</t>
         </is>
       </c>
-      <c r="C111" s="12" t="n">
+      <c r="C111" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="9" t="inlineStr">
+      <c r="A112" s="8" t="inlineStr">
         <is>
           <t>TRIA</t>
         </is>
@@ -3442,14 +3698,14 @@
           <t>F_TRIA</t>
         </is>
       </c>
-      <c r="C112" s="12" t="inlineStr">
+      <c r="C112" s="11" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="inlineStr">
+      <c r="A113" s="8" t="inlineStr">
         <is>
           <t>TRIS</t>
         </is>
@@ -3459,7 +3715,7 @@
           <t>F_TRIS</t>
         </is>
       </c>
-      <c r="C113" s="12" t="n">
+      <c r="C113" s="11" t="n">
         <v>1</v>
       </c>
     </row>

--- a/static_files/manual.xlsx
+++ b/static_files/manual.xlsx
@@ -6,10 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Besprechung" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Uebersicht" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Eventcodes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Abteilungsmapping" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="rehatis_test_07102026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Besprechung" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Uebersicht" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eventcodes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Abteilungsmapping" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="25">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -107,11 +108,6 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FF1F4E79"/>
       <sz val="10"/>
@@ -124,40 +120,68 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF1F4E79"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <i val="1"/>
       <color rgb="FF1F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <i val="1"/>
       <color rgb="FF333333"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Consolas"/>
-      <family val="3"/>
       <color rgb="FF1F2937"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="001F2937"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="30">
     <fill>
       <patternFill/>
     </fill>
@@ -191,6 +215,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -254,8 +284,80 @@
         <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFF9FAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F4F7"/>
+        <bgColor rgb="00F2F4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5597"/>
+        <bgColor rgb="002F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4C6E7"/>
+        <bgColor rgb="00B4C6E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9EEF4"/>
+        <bgColor rgb="00E9EEF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FAFB"/>
+        <bgColor rgb="00F9FAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00333333"/>
+        <bgColor rgb="00333333"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -290,6 +392,101 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -352,12 +549,70 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -406,41 +661,57 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -452,18 +723,57 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -559,6 +869,178 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>285750</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>20</col>
+      <colOff>230719</colOff>
+      <row>33</row>
+      <rowOff>172245</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Grafik 1"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="285750" y="762000"/>
+          <a:ext cx="15184969" cy="5696745"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>200025</colOff>
+      <row>37</row>
+      <rowOff>114300</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>192945</colOff>
+      <row>71</row>
+      <rowOff>48520</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Grafik 2"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="200025" y="7162800"/>
+          <a:ext cx="17518920" cy="6411220"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>152400</colOff>
+      <row>75</row>
+      <rowOff>133350</rowOff>
+    </from>
+    <to>
+      <col>18</col>
+      <colOff>676275</colOff>
+      <row>92</row>
+      <rowOff>152400</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Grafik 1"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="152400" y="14420850"/>
+          <a:ext cx="14239875" cy="3257550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>22</col>
+      <colOff>135602</colOff>
+      <row>136</row>
+      <rowOff>76929</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Grafik 4"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="762000" y="20764500"/>
+          <a:ext cx="16137602" cy="5220429"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -580,7 +1062,7 @@
       <grpSpPr>
         <a:xfrm rot="0">
           <a:off x="0" y="266700"/>
-          <a:ext cx="16099531" cy="8010798"/>
+          <a:ext cx="16404331" cy="8010798"/>
           <a:chOff x="0" y="47625"/>
           <a:chExt cx="16347181" cy="8010798"/>
         </a:xfrm>
@@ -699,7 +1181,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1061,20 +1543,97 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ39"/>
+  <dimension ref="B3:M108"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mapping für 1_21 anpassen</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Telefonnummer wird in rehatis nicht korrekt angezeigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Im Rehatis hat es ----------</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Reservationen mit Highdate sollen nicht im RehaTis erscheinen</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>korrekt</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Eventcode A05 mit Highdate</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Reservationen ohne Highdate sollen im RehaTis erscheinen</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>muss durch Willi auf korrekten Eventcode gemapt werden</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Eventcode A05 ohne Highdate --&gt; Umwandeln zu A14, damit er in Rehatis imporitert</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Eventcode A05 mit Highdate</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AJ63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col width="12.140625" customWidth="1" style="35" min="21" max="21"/>
-    <col width="0.7109375" customWidth="1" style="20" min="22" max="22"/>
+    <col width="16.28515625" customWidth="1" style="47" min="21" max="21"/>
+    <col width="1.140625" customWidth="1" style="20" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="46" t="inlineStr">
         <is>
           <t>Opale</t>
         </is>
       </c>
-      <c r="W1" s="36" t="inlineStr">
+      <c r="W1" s="48" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
@@ -1120,7 +1679,7 @@
     <row r="26">
       <c r="W26" s="21" t="inlineStr">
         <is>
-          <t>-Die Umsysteme (HL7) empfangen die Fach.OE heute im Feld PV1_3.4 Facility</t>
+          <t>-Die Umsysteme (HL7) empfangen die Fach.OE heute im Feld PV1_3.4 Facility, Ausnahme ist RehaTIS, wo die Fach:OE im Feld PV1_3.1 PointOfCare gesendet wird</t>
         </is>
       </c>
     </row>
@@ -1131,39 +1690,231 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="W28" s="21" t="inlineStr">
+        <is>
+          <t>-Orchestra entfernt ueberfall das F_ (--&gt; F_OHR1A wird zu OHR1A), Ausnahme ist Polypoint und RehaTIS, wo das F_ nicht entfernt wird (F_OHR1A)</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="J34" s="21" t="inlineStr">
-        <is>
-          <t>-Opale sendet das Feld Abteilung im HL7-File im Feld PV1_3.5 Location Status</t>
-        </is>
-      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>Opale</t>
+        </is>
+      </c>
+      <c r="K34" s="24" t="n"/>
+      <c r="L34" s="24" t="n"/>
+      <c r="M34" s="24" t="n"/>
+      <c r="N34" s="24" t="n"/>
+      <c r="O34" s="24" t="n"/>
+      <c r="P34" s="24" t="n"/>
+      <c r="Q34" s="24" t="n"/>
+      <c r="R34" s="25" t="n"/>
       <c r="AI34" s="22" t="n"/>
       <c r="AJ34" s="22" t="n"/>
     </row>
     <row r="35">
-      <c r="J35" s="21" t="inlineStr">
+      <c r="J35" s="26" t="n"/>
+      <c r="R35" s="27" t="n"/>
+    </row>
+    <row r="36">
+      <c r="J36" s="28" t="inlineStr">
+        <is>
+          <t>-Opale sendet das Feld Abteilung im HL7-File im Feld PV1_3.5 Location Status</t>
+        </is>
+      </c>
+      <c r="R36" s="27" t="n"/>
+    </row>
+    <row r="37">
+      <c r="J37" s="28" t="inlineStr">
         <is>
           <t>-Abteilung INES in Opale entspricht dem Feld Fach. OE in SAP</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="J36" s="21" t="inlineStr">
+      <c r="R37" s="27" t="n"/>
+    </row>
+    <row r="38">
+      <c r="J38" s="28" t="inlineStr">
         <is>
           <t>-Opale sendet das benutzerspezifische Feld Abteilung INES im HL7-File im Feld PV2_41.3 (spitalspezifisches Feld)</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="J37" s="21" t="inlineStr">
+      <c r="R38" s="27" t="n"/>
+    </row>
+    <row r="39">
+      <c r="J39" s="29" t="inlineStr">
         <is>
           <t>-Opale sendet Abteilung Ines im Format XXXX (z.B OHR1A) an die Umsysteme</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="P39" s="23" t="n"/>
-      <c r="Q39" s="23" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="30" t="n"/>
+      <c r="M39" s="30" t="n"/>
+      <c r="N39" s="30" t="n"/>
+      <c r="O39" s="30" t="n"/>
+      <c r="P39" s="31" t="n"/>
+      <c r="Q39" s="31" t="n"/>
+      <c r="R39" s="32" t="n"/>
+    </row>
+    <row r="41">
+      <c r="J41" s="33" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="K41" s="24" t="n"/>
+      <c r="L41" s="24" t="n"/>
+      <c r="M41" s="24" t="n"/>
+      <c r="N41" s="24" t="n"/>
+      <c r="O41" s="24" t="n"/>
+      <c r="P41" s="24" t="n"/>
+      <c r="Q41" s="24" t="n"/>
+      <c r="R41" s="24" t="n"/>
+      <c r="S41" s="24" t="n"/>
+      <c r="T41" s="24" t="n"/>
+      <c r="U41" s="25" t="n"/>
+    </row>
+    <row r="42">
+      <c r="J42" s="28" t="inlineStr">
+        <is>
+          <t>-Polypoint verwendet dat-File, Interflex verwendet txt-File, Ines verwendet HL7/Expopa10, alle anderen Systeme HL7</t>
+        </is>
+      </c>
+      <c r="U42" s="27" t="n"/>
+    </row>
+    <row r="43">
+      <c r="J43" s="28" t="inlineStr">
+        <is>
+          <t>-Die Fach. OE wird heute an die Umsysteme geliefert und entspricht der Abteilung INES in Opale</t>
+        </is>
+      </c>
+      <c r="U43" s="27" t="n"/>
+    </row>
+    <row r="44">
+      <c r="J44" s="28" t="inlineStr">
+        <is>
+          <t>-Die Umsysteme (HL7) empfangen die Fach.OE heute im Feld PV1_3.4 Facility, Ausnahme ist RehaTIS, wo die Fach:OE im Feld PV1_3.1 PointOfCare gesendet wird</t>
+        </is>
+      </c>
+      <c r="U44" s="27" t="n"/>
+    </row>
+    <row r="45">
+      <c r="J45" s="28" t="inlineStr">
+        <is>
+          <t>-SAP sendet heute die Fach. OE im Format F_XXXX (z.B F_OHR1A) an die Umsysteme</t>
+        </is>
+      </c>
+      <c r="U45" s="27" t="n"/>
+    </row>
+    <row r="46">
+      <c r="J46" s="29" t="inlineStr">
+        <is>
+          <t>-Orchestra entfernt ueberfall das F_ (--&gt; F_OHR1A wird zu OHR1A), Ausnahme ist Polypoint und RehaTIS, wo das F_ nicht entfernt wird (F_OHR1A)</t>
+        </is>
+      </c>
+      <c r="K46" s="30" t="n"/>
+      <c r="L46" s="30" t="n"/>
+      <c r="M46" s="30" t="n"/>
+      <c r="N46" s="30" t="n"/>
+      <c r="O46" s="30" t="n"/>
+      <c r="P46" s="30" t="n"/>
+      <c r="Q46" s="30" t="n"/>
+      <c r="R46" s="30" t="n"/>
+      <c r="S46" s="30" t="n"/>
+      <c r="T46" s="30" t="n"/>
+      <c r="U46" s="32" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Fragen:</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Warum verwendent wir für die Abteilunges INES ein kundenspezifisches Feld und nicht das Feld Abteilung?</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Warum sendet Opale die Abteilung im HL7 im PV1_3.5 Location Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Todos:</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Orchestralogik besprechen. IMHO muss Willi folgendes in Orchestra sicherstellen:</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Orchestralogik Opale</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Die für die Umsysteme wichtige Ines-Abteilung wird durch Opale in PV2_41.3 geliefert. </t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Willi muss diese aber für alle Umsysteme in PV1_3.4 liefern. Ausnahme RehaTIS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Für RehaTIS muss es in PV1_3.1 geliefert werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Dies Ines-Abteilung FR1 muss zu NRUR gemappt werden (alter Name SAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Alle Umsysteme kennen heute die Ines-Abteilung ohne F_ (weil dieses durch SAP-Orchestra entfernt wird.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ausnahme ist: Popypoint und RehaTIS, diese kennen die Umsysteme mit F_</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Willi muss bei Polypoint und RehaTIS jeweils ein F_ hinzufügen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1171,12 +1922,12 @@
     <mergeCell ref="W1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="32" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1192,8 +1943,8 @@
     <col width="60.7109375" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
     <col width="39.42578125" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
     <col width="18.5703125" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
-    <col width="11.42578125" customWidth="1" style="2" min="8" max="31"/>
-    <col width="11.42578125" customWidth="1" style="2" min="32" max="16384"/>
+    <col width="11.42578125" customWidth="1" style="2" min="8" max="35"/>
+    <col width="11.42578125" customWidth="1" style="2" min="36" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1238,7 +1989,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1" s="35">
+    <row r="2" ht="60" customHeight="1" s="47">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Diacos</t>
@@ -1345,7 +2096,7 @@
       <c r="C5" s="2" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Auf Paolo warten</t>
+          <t>Auf Paolo warten!</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1411,7 +2162,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="35">
+    <row r="8" ht="30" customHeight="1" s="47">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Interflex</t>
@@ -1427,14 +2178,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>(x)</t>
-        </is>
-      </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Interflex prüft bei ambulanten Fällen, ob die Abteilung in Interflex hinterlegt ist</t>
+          <t>Auf Willi warten!</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1574,6 +2320,11 @@
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>HL7</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Marina</t>
         </is>
       </c>
     </row>
@@ -1733,7 +2484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1742,12 +2493,12 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="37.28515625" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="35" min="1" max="1"/>
-    <col width="32.7109375" customWidth="1" style="35" min="2" max="2"/>
-    <col width="39.5703125" customWidth="1" style="35" min="3" max="4"/>
+    <col width="18" customWidth="1" style="47" min="1" max="1"/>
+    <col width="32.7109375" customWidth="1" style="47" min="2" max="2"/>
+    <col width="39.5703125" customWidth="1" style="47" min="3" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="35" thickBot="1">
+    <row r="1" ht="15.75" customHeight="1" s="47" thickBot="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
           <t>Event Code</t>
@@ -1764,7 +2515,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="35" thickBot="1">
+    <row r="2" ht="15.75" customHeight="1" s="47" thickBot="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
           <t>A01</t>
@@ -1781,7 +2532,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.25" customHeight="1" s="35" thickBot="1">
+    <row r="3" ht="29.25" customHeight="1" s="47" thickBot="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
           <t>A02</t>
@@ -1798,7 +2549,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" s="35" thickBot="1">
+    <row r="4" ht="15.75" customHeight="1" s="47" thickBot="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>A03</t>
@@ -1815,7 +2566,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="29.25" customHeight="1" s="35" thickBot="1">
+    <row r="5" ht="29.25" customHeight="1" s="47" thickBot="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>A04</t>
@@ -1832,7 +2583,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="29.25" customHeight="1" s="35" thickBot="1">
+    <row r="6" ht="29.25" customHeight="1" s="47" thickBot="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>A05</t>
@@ -1849,7 +2600,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="29.25" customHeight="1" s="35" thickBot="1">
+    <row r="7" ht="29.25" customHeight="1" s="47" thickBot="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>A08</t>
@@ -1866,7 +2617,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="35" thickBot="1">
+    <row r="8" ht="15.75" customHeight="1" s="47" thickBot="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>A11</t>
@@ -1883,7 +2634,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="35" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="47" thickBot="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>A12</t>
@@ -1900,7 +2651,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="35" thickBot="1">
+    <row r="10" ht="15.75" customHeight="1" s="47" thickBot="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>A13</t>
@@ -1917,7 +2668,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="33" customHeight="1" s="35" thickBot="1">
+    <row r="11" ht="33" customHeight="1" s="47" thickBot="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t>A14</t>
@@ -1934,7 +2685,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="35" thickBot="1">
+    <row r="12" ht="15.75" customHeight="1" s="47" thickBot="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
           <t>A28</t>
@@ -1951,7 +2702,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="29.25" customHeight="1" s="35" thickBot="1">
+    <row r="13" ht="29.25" customHeight="1" s="47" thickBot="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t>A31</t>
@@ -1968,7 +2719,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="29.25" customHeight="1" s="35" thickBot="1">
+    <row r="14" ht="29.25" customHeight="1" s="47" thickBot="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
           <t>A40</t>
@@ -1987,10 +2738,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1999,10 +2751,10 @@
   <dimension ref="A1:Q113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col width="29.28515625" bestFit="1" customWidth="1" style="35" min="1" max="1"/>
-    <col width="16.7109375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
+    <col width="29.28515625" bestFit="1" customWidth="1" style="47" min="1" max="1"/>
+    <col width="16.7109375" bestFit="1" customWidth="1" style="47" min="2" max="2"/>
     <col width="23.85546875" bestFit="1" customWidth="1" style="11" min="3" max="3"/>
-    <col width="3.42578125" customWidth="1" style="35" min="5" max="5"/>
+    <col width="3.42578125" customWidth="1" style="47" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2021,7 +2773,7 @@
           <t>Stationär(1), Ambulant(2)</t>
         </is>
       </c>
-      <c r="F1" s="37" t="inlineStr">
+      <c r="F1" s="49" t="inlineStr">
         <is>
           <t>Ab 01.01.2027 wird Opale als ERP eingesetzt. Alle an Orchestra angeschlossende Umsysteme kennen aber die Abteilungsnahmen aus SAP. In der Folge müssen die von Opale gesendeten Abteilungsnahmen (Spalte A) auf den ehemaligen SAP-Abteilungsnahmen (Spalte B) von Orchestra transformiert werden:
 Transformationsregel:
@@ -3546,11 +4298,7 @@
       <c r="C102" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>(Ausname!)</t>
-        </is>
-      </c>
+      <c r="D102" s="6" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">

--- a/static_files/manual.xlsx
+++ b/static_files/manual.xlsx
@@ -181,7 +181,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="30">
+  <fills count="28">
     <fill>
       <patternFill/>
     </fill>
@@ -282,18 +282,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF333333"/>
         <bgColor rgb="FF333333"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFF9FAFB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -612,7 +600,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -707,12 +695,6 @@
     <xf numFmtId="0" fontId="19" fillId="9" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -735,43 +717,43 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="26" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1623,17 +1605,17 @@
   <dimension ref="A1:AJ63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col width="16.28515625" customWidth="1" style="47" min="21" max="21"/>
+    <col width="16.28515625" customWidth="1" style="45" min="21" max="21"/>
     <col width="1.140625" customWidth="1" style="20" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="46" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>Opale</t>
         </is>
       </c>
-      <c r="W1" s="48" t="inlineStr">
+      <c r="W1" s="46" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
@@ -1943,8 +1925,8 @@
     <col width="60.7109375" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
     <col width="39.42578125" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
     <col width="18.5703125" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
-    <col width="11.42578125" customWidth="1" style="2" min="8" max="35"/>
-    <col width="11.42578125" customWidth="1" style="2" min="36" max="16384"/>
+    <col width="11.42578125" customWidth="1" style="2" min="8" max="37"/>
+    <col width="11.42578125" customWidth="1" style="2" min="38" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1989,7 +1971,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1" s="47">
+    <row r="2" ht="60" customHeight="1" s="45">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Diacos</t>
@@ -2106,7 +2088,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>HL7 (neu Expopa10)</t>
+          <t>Expopa10</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2144,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="47">
+    <row r="8" ht="30" customHeight="1" s="45">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Interflex</t>
@@ -2320,11 +2302,6 @@
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>HL7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Marina</t>
         </is>
       </c>
     </row>
@@ -2493,12 +2470,12 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="37.28515625" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="47" min="1" max="1"/>
-    <col width="32.7109375" customWidth="1" style="47" min="2" max="2"/>
-    <col width="39.5703125" customWidth="1" style="47" min="3" max="4"/>
+    <col width="18" customWidth="1" style="45" min="1" max="1"/>
+    <col width="32.7109375" customWidth="1" style="45" min="2" max="2"/>
+    <col width="39.5703125" customWidth="1" style="45" min="3" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="47" thickBot="1">
+    <row r="1" ht="15.75" customHeight="1" s="45" thickBot="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
           <t>Event Code</t>
@@ -2515,7 +2492,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="47" thickBot="1">
+    <row r="2" ht="15.75" customHeight="1" s="45" thickBot="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
           <t>A01</t>
@@ -2532,7 +2509,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.25" customHeight="1" s="47" thickBot="1">
+    <row r="3" ht="29.25" customHeight="1" s="45" thickBot="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
           <t>A02</t>
@@ -2549,7 +2526,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" s="47" thickBot="1">
+    <row r="4" ht="15.75" customHeight="1" s="45" thickBot="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>A03</t>
@@ -2566,7 +2543,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="29.25" customHeight="1" s="47" thickBot="1">
+    <row r="5" ht="29.25" customHeight="1" s="45" thickBot="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>A04</t>
@@ -2583,7 +2560,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="29.25" customHeight="1" s="47" thickBot="1">
+    <row r="6" ht="29.25" customHeight="1" s="45" thickBot="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>A05</t>
@@ -2600,7 +2577,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="29.25" customHeight="1" s="47" thickBot="1">
+    <row r="7" ht="29.25" customHeight="1" s="45" thickBot="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>A08</t>
@@ -2617,7 +2594,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="47" thickBot="1">
+    <row r="8" ht="15.75" customHeight="1" s="45" thickBot="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>A11</t>
@@ -2634,7 +2611,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="47" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="45" thickBot="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>A12</t>
@@ -2651,7 +2628,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="47" thickBot="1">
+    <row r="10" ht="15.75" customHeight="1" s="45" thickBot="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>A13</t>
@@ -2668,7 +2645,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="33" customHeight="1" s="47" thickBot="1">
+    <row r="11" ht="33" customHeight="1" s="45" thickBot="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t>A14</t>
@@ -2685,7 +2662,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="47" thickBot="1">
+    <row r="12" ht="15.75" customHeight="1" s="45" thickBot="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
           <t>A28</t>
@@ -2702,7 +2679,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="29.25" customHeight="1" s="47" thickBot="1">
+    <row r="13" ht="29.25" customHeight="1" s="45" thickBot="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t>A31</t>
@@ -2719,7 +2696,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="29.25" customHeight="1" s="47" thickBot="1">
+    <row r="14" ht="29.25" customHeight="1" s="45" thickBot="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
           <t>A40</t>
@@ -2751,10 +2728,10 @@
   <dimension ref="A1:Q113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col width="29.28515625" bestFit="1" customWidth="1" style="47" min="1" max="1"/>
-    <col width="16.7109375" bestFit="1" customWidth="1" style="47" min="2" max="2"/>
+    <col width="29.28515625" bestFit="1" customWidth="1" style="45" min="1" max="1"/>
+    <col width="16.7109375" bestFit="1" customWidth="1" style="45" min="2" max="2"/>
     <col width="23.85546875" bestFit="1" customWidth="1" style="11" min="3" max="3"/>
-    <col width="3.42578125" customWidth="1" style="47" min="5" max="5"/>
+    <col width="3.42578125" customWidth="1" style="45" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2773,7 +2750,7 @@
           <t>Stationär(1), Ambulant(2)</t>
         </is>
       </c>
-      <c r="F1" s="49" t="inlineStr">
+      <c r="F1" s="47" t="inlineStr">
         <is>
           <t>Ab 01.01.2027 wird Opale als ERP eingesetzt. Alle an Orchestra angeschlossende Umsysteme kennen aber die Abteilungsnahmen aus SAP. In der Folge müssen die von Opale gesendeten Abteilungsnahmen (Spalte A) auf den ehemaligen SAP-Abteilungsnahmen (Spalte B) von Orchestra transformiert werden:
 Transformationsregel:

--- a/static_files/manual.xlsx
+++ b/static_files/manual.xlsx
@@ -1925,8 +1925,8 @@
     <col width="60.7109375" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
     <col width="39.42578125" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
     <col width="18.5703125" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
-    <col width="11.42578125" customWidth="1" style="2" min="8" max="37"/>
-    <col width="11.42578125" customWidth="1" style="2" min="38" max="16384"/>
+    <col width="11.42578125" customWidth="1" style="2" min="8" max="38"/>
+    <col width="11.42578125" customWidth="1" style="2" min="39" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
